--- a/research/traditional_assets/database/data/greece/greece_air_transport.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="atse_aegn" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.109</v>
+        <v>0.0191</v>
+      </c>
+      <c r="E2">
+        <v>0.0563</v>
       </c>
       <c r="G2">
-        <v>-0.3598151736473394</v>
+        <v>0.04344556771660121</v>
       </c>
       <c r="H2">
-        <v>-0.3598151736473394</v>
+        <v>0.04344556771660121</v>
       </c>
       <c r="I2">
-        <v>0.05947235057385601</v>
+        <v>0.09349151975937839</v>
       </c>
       <c r="J2">
-        <v>0.05947235057385601</v>
+        <v>0.07901018150668657</v>
       </c>
       <c r="K2">
-        <v>-13.8</v>
+        <v>68</v>
       </c>
       <c r="L2">
-        <v>-0.02056938440900283</v>
+        <v>0.05681343470632467</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,76 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>615.7</v>
+        <v>557.9</v>
       </c>
       <c r="V2">
-        <v>1.249644814288614</v>
+        <v>1.094350725774814</v>
       </c>
       <c r="W2">
-        <v>-0.1165540540540541</v>
+        <v>0.2616390919584456</v>
       </c>
       <c r="X2">
-        <v>0.1840564519063034</v>
+        <v>0.2797256145002235</v>
       </c>
       <c r="Y2">
-        <v>-0.3006105059603574</v>
+        <v>-0.01808652254177789</v>
       </c>
       <c r="Z2">
-        <v>1.575992482969227</v>
+        <v>2.234690067214339</v>
       </c>
       <c r="AA2">
-        <v>0.09372797744890768</v>
+        <v>0.1765632678217946</v>
       </c>
       <c r="AB2">
-        <v>0.09419723542831664</v>
+        <v>0.1398942599894453</v>
       </c>
       <c r="AC2">
-        <v>-0.0004692579794089574</v>
+        <v>0.03666900783234925</v>
       </c>
       <c r="AD2">
-        <v>891.4</v>
+        <v>1038</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>891.4</v>
+        <v>1038</v>
       </c>
       <c r="AG2">
-        <v>275.6999999999999</v>
+        <v>480.1</v>
       </c>
       <c r="AH2">
-        <v>0.6440286106495196</v>
+        <v>0.6706292802687686</v>
       </c>
       <c r="AI2">
-        <v>0.7742551897854599</v>
+        <v>0.7460648314525983</v>
       </c>
       <c r="AJ2">
-        <v>0.3587975013014055</v>
+        <v>0.4849984846954238</v>
       </c>
       <c r="AK2">
-        <v>0.5147498132935026</v>
+        <v>0.576073914086873</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>22.6</v>
       </c>
       <c r="AM2">
-        <v>-28.4</v>
+        <v>22.156</v>
       </c>
       <c r="AN2">
-        <v>20.92488262910798</v>
+        <v>8.543209876543211</v>
+      </c>
+      <c r="AO2">
+        <v>4.951327433628318</v>
       </c>
       <c r="AP2">
-        <v>6.471830985915491</v>
+        <v>3.951440329218107</v>
       </c>
       <c r="AQ2">
-        <v>-1.404929577464789</v>
+        <v>5.050550640909911</v>
       </c>
     </row>
     <row r="3">
@@ -713,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.109</v>
+        <v>0.0191</v>
+      </c>
+      <c r="E3">
+        <v>0.0563</v>
       </c>
       <c r="G3">
-        <v>-0.3598151736473394</v>
+        <v>0.04344556771660121</v>
       </c>
       <c r="H3">
-        <v>-0.3598151736473394</v>
+        <v>0.04344556771660121</v>
       </c>
       <c r="I3">
-        <v>0.05947235057385601</v>
+        <v>0.09349151975937839</v>
       </c>
       <c r="J3">
-        <v>0.05947235057385601</v>
+        <v>0.07901018150668657</v>
       </c>
       <c r="K3">
-        <v>-13.8</v>
+        <v>68</v>
       </c>
       <c r="L3">
-        <v>-0.02056938440900283</v>
+        <v>0.05681343470632467</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,76 +760,8780 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>615.7</v>
+        <v>557.9</v>
       </c>
       <c r="V3">
-        <v>1.249644814288614</v>
+        <v>1.094350725774814</v>
       </c>
       <c r="W3">
-        <v>-0.1165540540540541</v>
+        <v>0.2616390919584456</v>
       </c>
       <c r="X3">
-        <v>0.1840564519063034</v>
+        <v>0.2797256145002235</v>
       </c>
       <c r="Y3">
-        <v>-0.3006105059603574</v>
+        <v>-0.01808652254177789</v>
       </c>
       <c r="Z3">
-        <v>1.575992482969227</v>
+        <v>2.234690067214339</v>
       </c>
       <c r="AA3">
-        <v>0.09372797744890768</v>
+        <v>0.1765632678217946</v>
       </c>
       <c r="AB3">
-        <v>0.09419723542831664</v>
+        <v>0.1398942599894453</v>
       </c>
       <c r="AC3">
-        <v>-0.0004692579794089574</v>
+        <v>0.03666900783234925</v>
       </c>
       <c r="AD3">
-        <v>891.4</v>
+        <v>1038</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>891.4</v>
+        <v>1038</v>
       </c>
       <c r="AG3">
-        <v>275.6999999999999</v>
+        <v>480.1</v>
       </c>
       <c r="AH3">
-        <v>0.6440286106495196</v>
+        <v>0.6706292802687686</v>
       </c>
       <c r="AI3">
-        <v>0.7742551897854599</v>
+        <v>0.7460648314525983</v>
       </c>
       <c r="AJ3">
-        <v>0.3587975013014055</v>
+        <v>0.4849984846954238</v>
       </c>
       <c r="AK3">
-        <v>0.5147498132935026</v>
+        <v>0.576073914086873</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>22.6</v>
       </c>
       <c r="AM3">
-        <v>-28.4</v>
+        <v>22.156</v>
       </c>
       <c r="AN3">
-        <v>20.92488262910798</v>
+        <v>8.543209876543211</v>
+      </c>
+      <c r="AO3">
+        <v>4.951327433628318</v>
       </c>
       <c r="AP3">
-        <v>6.471830985915491</v>
+        <v>3.951440329218107</v>
       </c>
       <c r="AQ3">
-        <v>-1.404929577464789</v>
+        <v>5.050550640909911</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aegean Airlines S.A. (ATSE:AEGN)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ATSE:AEGN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.670629280268769</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>509.8</v>
+      </c>
+      <c r="H2">
+        <v>1552.16945781679</v>
+      </c>
+      <c r="I2">
+        <v>989.9</v>
+      </c>
+      <c r="J2">
+        <v>1009.74745781679</v>
+      </c>
+      <c r="K2">
+        <v>1038</v>
+      </c>
+      <c r="L2">
+        <v>15.478</v>
+      </c>
+      <c r="M2">
+        <v>0.139894259989445</v>
+      </c>
+      <c r="N2">
+        <v>0.137799265310055</v>
+      </c>
+      <c r="O2">
+        <v>0.0712179357798165</v>
+      </c>
+      <c r="P2">
+        <v>0.520231709523194</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.279725614500223</v>
+      </c>
+      <c r="T2">
+        <v>0.133936311328104</v>
+      </c>
+      <c r="U2">
+        <v>1.98755626630766</v>
+      </c>
+      <c r="V2">
+        <v>0.784842957133537</v>
+      </c>
+      <c r="W2">
+        <v>-5.356930667032024</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>509.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.1212170033041622</v>
+      </c>
+      <c r="AC2">
+        <v>0.09130504587155963</v>
+      </c>
+      <c r="AD2">
+        <v>0.22</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>121.5</v>
+      </c>
+      <c r="AH2">
+        <v>141.3</v>
+      </c>
+      <c r="AI2">
+        <v>23.75</v>
+      </c>
+      <c r="AJ2">
+        <v>1038</v>
+      </c>
+      <c r="AK2">
+        <v>1038</v>
+      </c>
+      <c r="AL2">
+        <v>22.6</v>
+      </c>
+      <c r="AM2">
+        <v>1038</v>
+      </c>
+      <c r="AN2">
+        <v>557.9</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-1038</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>557.9</v>
+      </c>
+      <c r="H2">
+        <v>509.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>121.5</v>
+      </c>
+      <c r="K2">
+        <v>141.3</v>
+      </c>
+      <c r="L2">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="O2">
+        <v>-4.356000000000002</v>
+      </c>
+      <c r="P2">
+        <v>-15.44400000000001</v>
+      </c>
+      <c r="Q2">
+        <v>125.856</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1377992653100552</v>
+      </c>
+      <c r="C3">
+        <v>1552.169457816791</v>
+      </c>
+      <c r="D3">
+        <v>1009.747457816791</v>
+      </c>
+      <c r="E3">
+        <v>-1022.522</v>
+      </c>
+      <c r="F3">
+        <v>15.478</v>
+      </c>
+      <c r="G3">
+        <v>557.9</v>
+      </c>
+      <c r="H3">
+        <v>509.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>121.5</v>
+      </c>
+      <c r="K3">
+        <v>141.3</v>
+      </c>
+      <c r="L3">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M3">
+        <v>3.6961464</v>
+      </c>
+      <c r="N3">
+        <v>-23.49614640000001</v>
+      </c>
+      <c r="O3">
+        <v>-5.169152208000002</v>
+      </c>
+      <c r="P3">
+        <v>-18.32699419200001</v>
+      </c>
+      <c r="Q3">
+        <v>122.973005808</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1339363113281043</v>
+      </c>
+      <c r="T3">
+        <v>0.7848429571335366</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-1.178524746747045</v>
+      </c>
+      <c r="W3">
+        <v>0.5202317095231944</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-5.356930667032024</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1397992653100552</v>
+      </c>
+      <c r="C4">
+        <v>1517.727053560366</v>
+      </c>
+      <c r="D4">
+        <v>990.7830535603661</v>
+      </c>
+      <c r="E4">
+        <v>-1007.044</v>
+      </c>
+      <c r="F4">
+        <v>30.956</v>
+      </c>
+      <c r="G4">
+        <v>557.9</v>
+      </c>
+      <c r="H4">
+        <v>509.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>121.5</v>
+      </c>
+      <c r="K4">
+        <v>141.3</v>
+      </c>
+      <c r="L4">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M4">
+        <v>7.3922928</v>
+      </c>
+      <c r="N4">
+        <v>-27.19229280000001</v>
+      </c>
+      <c r="O4">
+        <v>-5.982304416000002</v>
+      </c>
+      <c r="P4">
+        <v>-21.20998838400001</v>
+      </c>
+      <c r="Q4">
+        <v>120.090011616</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1349070900151258</v>
+      </c>
+      <c r="T4">
+        <v>0.7928515587369401</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-0.5892623733735225</v>
+      </c>
+      <c r="W4">
+        <v>0.3795158547615972</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-2.678465333516012</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1417992653100552</v>
+      </c>
+      <c r="C5">
+        <v>1483.983870615682</v>
+      </c>
+      <c r="D5">
+        <v>972.5178706156818</v>
+      </c>
+      <c r="E5">
+        <v>-991.566</v>
+      </c>
+      <c r="F5">
+        <v>46.434</v>
+      </c>
+      <c r="G5">
+        <v>557.9</v>
+      </c>
+      <c r="H5">
+        <v>509.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>121.5</v>
+      </c>
+      <c r="K5">
+        <v>141.3</v>
+      </c>
+      <c r="L5">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M5">
+        <v>11.0884392</v>
+      </c>
+      <c r="N5">
+        <v>-30.88843920000001</v>
+      </c>
+      <c r="O5">
+        <v>-6.795456624000002</v>
+      </c>
+      <c r="P5">
+        <v>-24.09298257600001</v>
+      </c>
+      <c r="Q5">
+        <v>117.207017424</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1358978847575498</v>
+      </c>
+      <c r="T5">
+        <v>0.8010252861465993</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-0.392841582249015</v>
+      </c>
+      <c r="W5">
+        <v>0.3326105698410648</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-1.785643555677341</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1437992653100552</v>
+      </c>
+      <c r="C6">
+        <v>1450.901938334609</v>
+      </c>
+      <c r="D6">
+        <v>954.9139383346093</v>
+      </c>
+      <c r="E6">
+        <v>-976.088</v>
+      </c>
+      <c r="F6">
+        <v>61.912</v>
+      </c>
+      <c r="G6">
+        <v>557.9</v>
+      </c>
+      <c r="H6">
+        <v>509.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>121.5</v>
+      </c>
+      <c r="K6">
+        <v>141.3</v>
+      </c>
+      <c r="L6">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M6">
+        <v>14.7845856</v>
+      </c>
+      <c r="N6">
+        <v>-34.58458560000001</v>
+      </c>
+      <c r="O6">
+        <v>-7.608608832000002</v>
+      </c>
+      <c r="P6">
+        <v>-26.97597676800001</v>
+      </c>
+      <c r="Q6">
+        <v>114.324023232</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1369093210571076</v>
+      </c>
+      <c r="T6">
+        <v>0.8093692995439596</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-0.2946311866867612</v>
+      </c>
+      <c r="W6">
+        <v>0.3091579273807986</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-1.339232666758006</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1457992653100552</v>
+      </c>
+      <c r="C7">
+        <v>1418.445986475036</v>
+      </c>
+      <c r="D7">
+        <v>937.9359864750364</v>
+      </c>
+      <c r="E7">
+        <v>-960.61</v>
+      </c>
+      <c r="F7">
+        <v>77.39</v>
+      </c>
+      <c r="G7">
+        <v>557.9</v>
+      </c>
+      <c r="H7">
+        <v>509.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>121.5</v>
+      </c>
+      <c r="K7">
+        <v>141.3</v>
+      </c>
+      <c r="L7">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M7">
+        <v>18.480732</v>
+      </c>
+      <c r="N7">
+        <v>-38.28073200000001</v>
+      </c>
+      <c r="O7">
+        <v>-8.421761040000002</v>
+      </c>
+      <c r="P7">
+        <v>-29.85897096000001</v>
+      </c>
+      <c r="Q7">
+        <v>111.44102904</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1379420507524456</v>
+      </c>
+      <c r="T7">
+        <v>0.8178889763812646</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-0.235704949349409</v>
+      </c>
+      <c r="W7">
+        <v>0.2950863419046389</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-1.071386133406405</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1477992653100552</v>
+      </c>
+      <c r="C8">
+        <v>1386.583209334286</v>
+      </c>
+      <c r="D8">
+        <v>921.5512093342865</v>
+      </c>
+      <c r="E8">
+        <v>-945.1320000000001</v>
+      </c>
+      <c r="F8">
+        <v>92.86799999999999</v>
+      </c>
+      <c r="G8">
+        <v>557.9</v>
+      </c>
+      <c r="H8">
+        <v>509.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>121.5</v>
+      </c>
+      <c r="K8">
+        <v>141.3</v>
+      </c>
+      <c r="L8">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M8">
+        <v>22.1768784</v>
+      </c>
+      <c r="N8">
+        <v>-41.97687840000001</v>
+      </c>
+      <c r="O8">
+        <v>-9.234913248000002</v>
+      </c>
+      <c r="P8">
+        <v>-32.74196515200001</v>
+      </c>
+      <c r="Q8">
+        <v>108.558034848</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1389967534200248</v>
+      </c>
+      <c r="T8">
+        <v>0.8265899229385121</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-0.1964207911245075</v>
+      </c>
+      <c r="W8">
+        <v>0.2857052849205324</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-0.8928217778386704</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1497992653100552</v>
+      </c>
+      <c r="C9">
+        <v>1355.283054180162</v>
+      </c>
+      <c r="D9">
+        <v>905.7290541801623</v>
+      </c>
+      <c r="E9">
+        <v>-929.654</v>
+      </c>
+      <c r="F9">
+        <v>108.346</v>
+      </c>
+      <c r="G9">
+        <v>557.9</v>
+      </c>
+      <c r="H9">
+        <v>509.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>121.5</v>
+      </c>
+      <c r="K9">
+        <v>141.3</v>
+      </c>
+      <c r="L9">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M9">
+        <v>25.8730248</v>
+      </c>
+      <c r="N9">
+        <v>-45.67302480000001</v>
+      </c>
+      <c r="O9">
+        <v>-10.048065456</v>
+      </c>
+      <c r="P9">
+        <v>-35.62495934400001</v>
+      </c>
+      <c r="Q9">
+        <v>105.675040656</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1400741378654014</v>
+      </c>
+      <c r="T9">
+        <v>0.835477986626023</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-0.1683606781067207</v>
+      </c>
+      <c r="W9">
+        <v>0.2790045299318849</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-0.7652758095760033</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1517992653100552</v>
+      </c>
+      <c r="C10">
+        <v>1324.517031108739</v>
+      </c>
+      <c r="D10">
+        <v>890.4410311087391</v>
+      </c>
+      <c r="E10">
+        <v>-914.176</v>
+      </c>
+      <c r="F10">
+        <v>123.824</v>
+      </c>
+      <c r="G10">
+        <v>557.9</v>
+      </c>
+      <c r="H10">
+        <v>509.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>121.5</v>
+      </c>
+      <c r="K10">
+        <v>141.3</v>
+      </c>
+      <c r="L10">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M10">
+        <v>29.5691712</v>
+      </c>
+      <c r="N10">
+        <v>-49.36917120000001</v>
+      </c>
+      <c r="O10">
+        <v>-10.861217664</v>
+      </c>
+      <c r="P10">
+        <v>-38.50795353600001</v>
+      </c>
+      <c r="Q10">
+        <v>102.792046464</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1411749437117644</v>
+      </c>
+      <c r="T10">
+        <v>0.8445592690893492</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-0.1473155933433806</v>
+      </c>
+      <c r="W10">
+        <v>0.2739789636903993</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-0.6696163333790028</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1537992653100552</v>
+      </c>
+      <c r="C11">
+        <v>1294.258541839251</v>
+      </c>
+      <c r="D11">
+        <v>875.660541839251</v>
+      </c>
+      <c r="E11">
+        <v>-898.698</v>
+      </c>
+      <c r="F11">
+        <v>139.302</v>
+      </c>
+      <c r="G11">
+        <v>557.9</v>
+      </c>
+      <c r="H11">
+        <v>509.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>121.5</v>
+      </c>
+      <c r="K11">
+        <v>141.3</v>
+      </c>
+      <c r="L11">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M11">
+        <v>33.2653176</v>
+      </c>
+      <c r="N11">
+        <v>-53.06531760000001</v>
+      </c>
+      <c r="O11">
+        <v>-11.674369872</v>
+      </c>
+      <c r="P11">
+        <v>-41.39094772800001</v>
+      </c>
+      <c r="Q11">
+        <v>99.909052272</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1422999430932124</v>
+      </c>
+      <c r="T11">
+        <v>0.8538401401782433</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-0.130947194083005</v>
+      </c>
+      <c r="W11">
+        <v>0.2700701899470216</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-0.5952145185591136</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1557992653100552</v>
+      </c>
+      <c r="C12">
+        <v>1264.482725281641</v>
+      </c>
+      <c r="D12">
+        <v>861.3627252816406</v>
+      </c>
+      <c r="E12">
+        <v>-883.22</v>
+      </c>
+      <c r="F12">
+        <v>154.78</v>
+      </c>
+      <c r="G12">
+        <v>557.9</v>
+      </c>
+      <c r="H12">
+        <v>509.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>121.5</v>
+      </c>
+      <c r="K12">
+        <v>141.3</v>
+      </c>
+      <c r="L12">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M12">
+        <v>36.961464</v>
+      </c>
+      <c r="N12">
+        <v>-56.76146400000001</v>
+      </c>
+      <c r="O12">
+        <v>-12.48752208</v>
+      </c>
+      <c r="P12">
+        <v>-44.27394192000001</v>
+      </c>
+      <c r="Q12">
+        <v>97.02605808</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1434499424609147</v>
+      </c>
+      <c r="T12">
+        <v>0.8633272528468903</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-0.1178524746747045</v>
+      </c>
+      <c r="W12">
+        <v>0.2669431709523195</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-0.5356930667032023</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1577992653100552</v>
+      </c>
+      <c r="C13">
+        <v>1235.166317990512</v>
+      </c>
+      <c r="D13">
+        <v>847.5243179905115</v>
+      </c>
+      <c r="E13">
+        <v>-867.742</v>
+      </c>
+      <c r="F13">
+        <v>170.258</v>
+      </c>
+      <c r="G13">
+        <v>557.9</v>
+      </c>
+      <c r="H13">
+        <v>509.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>121.5</v>
+      </c>
+      <c r="K13">
+        <v>141.3</v>
+      </c>
+      <c r="L13">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M13">
+        <v>40.6576104</v>
+      </c>
+      <c r="N13">
+        <v>-60.45761040000001</v>
+      </c>
+      <c r="O13">
+        <v>-13.300674288</v>
+      </c>
+      <c r="P13">
+        <v>-47.15693611200001</v>
+      </c>
+      <c r="Q13">
+        <v>94.143063888</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1446257845110374</v>
+      </c>
+      <c r="T13">
+        <v>0.8730275590586531</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.1071386133406404</v>
+      </c>
+      <c r="W13">
+        <v>0.2643847008657449</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-0.4869936970029112</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1597992653100552</v>
+      </c>
+      <c r="C14">
+        <v>1206.287527857834</v>
+      </c>
+      <c r="D14">
+        <v>834.1235278578341</v>
+      </c>
+      <c r="E14">
+        <v>-852.264</v>
+      </c>
+      <c r="F14">
+        <v>185.736</v>
+      </c>
+      <c r="G14">
+        <v>557.9</v>
+      </c>
+      <c r="H14">
+        <v>509.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>121.5</v>
+      </c>
+      <c r="K14">
+        <v>141.3</v>
+      </c>
+      <c r="L14">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M14">
+        <v>44.3537568</v>
+      </c>
+      <c r="N14">
+        <v>-64.15375680000001</v>
+      </c>
+      <c r="O14">
+        <v>-14.113826496</v>
+      </c>
+      <c r="P14">
+        <v>-50.03993030400001</v>
+      </c>
+      <c r="Q14">
+        <v>91.260069696</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1458283502441174</v>
+      </c>
+      <c r="T14">
+        <v>0.8829483267752287</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.09821039556225375</v>
+      </c>
+      <c r="W14">
+        <v>0.2622526424602662</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-0.4464108889193352</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1617992653100552</v>
+      </c>
+      <c r="C15">
+        <v>1177.825919601921</v>
+      </c>
+      <c r="D15">
+        <v>821.1399196019212</v>
+      </c>
+      <c r="E15">
+        <v>-836.7860000000001</v>
+      </c>
+      <c r="F15">
+        <v>201.214</v>
+      </c>
+      <c r="G15">
+        <v>557.9</v>
+      </c>
+      <c r="H15">
+        <v>509.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>121.5</v>
+      </c>
+      <c r="K15">
+        <v>141.3</v>
+      </c>
+      <c r="L15">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M15">
+        <v>48.0499032</v>
+      </c>
+      <c r="N15">
+        <v>-67.84990320000001</v>
+      </c>
+      <c r="O15">
+        <v>-14.926978704</v>
+      </c>
+      <c r="P15">
+        <v>-52.92292449600001</v>
+      </c>
+      <c r="Q15">
+        <v>88.377075504</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1470585611664635</v>
+      </c>
+      <c r="T15">
+        <v>0.8930971581174728</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.09065574974977268</v>
+      </c>
+      <c r="W15">
+        <v>0.2604485930402457</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-0.412071589771694</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1637992653100552</v>
+      </c>
+      <c r="C16">
+        <v>1149.762310787062</v>
+      </c>
+      <c r="D16">
+        <v>808.5543107870617</v>
+      </c>
+      <c r="E16">
+        <v>-821.308</v>
+      </c>
+      <c r="F16">
+        <v>216.692</v>
+      </c>
+      <c r="G16">
+        <v>557.9</v>
+      </c>
+      <c r="H16">
+        <v>509.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>121.5</v>
+      </c>
+      <c r="K16">
+        <v>141.3</v>
+      </c>
+      <c r="L16">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M16">
+        <v>51.74604960000001</v>
+      </c>
+      <c r="N16">
+        <v>-71.54604960000002</v>
+      </c>
+      <c r="O16">
+        <v>-15.740130912</v>
+      </c>
+      <c r="P16">
+        <v>-55.80591868800002</v>
+      </c>
+      <c r="Q16">
+        <v>85.49408131199999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1483173816451434</v>
+      </c>
+      <c r="T16">
+        <v>0.9034820087932574</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.08418033905336035</v>
+      </c>
+      <c r="W16">
+        <v>0.2589022649659425</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-0.3826379047880015</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1657992653100552</v>
+      </c>
+      <c r="C17">
+        <v>1122.078677261052</v>
+      </c>
+      <c r="D17">
+        <v>796.3486772610519</v>
+      </c>
+      <c r="E17">
+        <v>-805.83</v>
+      </c>
+      <c r="F17">
+        <v>232.17</v>
+      </c>
+      <c r="G17">
+        <v>557.9</v>
+      </c>
+      <c r="H17">
+        <v>509.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>121.5</v>
+      </c>
+      <c r="K17">
+        <v>141.3</v>
+      </c>
+      <c r="L17">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M17">
+        <v>55.442196</v>
+      </c>
+      <c r="N17">
+        <v>-75.24219600000001</v>
+      </c>
+      <c r="O17">
+        <v>-16.55328312</v>
+      </c>
+      <c r="P17">
+        <v>-58.68891288</v>
+      </c>
+      <c r="Q17">
+        <v>82.61108712000001</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1496058214292039</v>
+      </c>
+      <c r="T17">
+        <v>0.9141112088967074</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.07856831644980299</v>
+      </c>
+      <c r="W17">
+        <v>0.257562113968213</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-0.3571287111354682</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1677992653100552</v>
+      </c>
+      <c r="C18">
+        <v>1094.75806703023</v>
+      </c>
+      <c r="D18">
+        <v>784.5060670302297</v>
+      </c>
+      <c r="E18">
+        <v>-790.352</v>
+      </c>
+      <c r="F18">
+        <v>247.648</v>
+      </c>
+      <c r="G18">
+        <v>557.9</v>
+      </c>
+      <c r="H18">
+        <v>509.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>121.5</v>
+      </c>
+      <c r="K18">
+        <v>141.3</v>
+      </c>
+      <c r="L18">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M18">
+        <v>59.1383424</v>
+      </c>
+      <c r="N18">
+        <v>-78.93834240000001</v>
+      </c>
+      <c r="O18">
+        <v>-17.366435328</v>
+      </c>
+      <c r="P18">
+        <v>-61.57190707200001</v>
+      </c>
+      <c r="Q18">
+        <v>79.728092928</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1509249383509801</v>
+      </c>
+      <c r="T18">
+        <v>0.9249934851930968</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.07365779667169031</v>
+      </c>
+      <c r="W18">
+        <v>0.2563894818451997</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-0.3348081666895015</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1697992653100552</v>
+      </c>
+      <c r="C19">
+        <v>1067.784521706564</v>
+      </c>
+      <c r="D19">
+        <v>773.0105217065643</v>
+      </c>
+      <c r="E19">
+        <v>-774.874</v>
+      </c>
+      <c r="F19">
+        <v>263.126</v>
+      </c>
+      <c r="G19">
+        <v>557.9</v>
+      </c>
+      <c r="H19">
+        <v>509.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>121.5</v>
+      </c>
+      <c r="K19">
+        <v>141.3</v>
+      </c>
+      <c r="L19">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M19">
+        <v>62.83448880000001</v>
+      </c>
+      <c r="N19">
+        <v>-82.63448880000001</v>
+      </c>
+      <c r="O19">
+        <v>-18.179587536</v>
+      </c>
+      <c r="P19">
+        <v>-64.45490126400001</v>
+      </c>
+      <c r="Q19">
+        <v>76.845098736</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1522758412226787</v>
+      </c>
+      <c r="T19">
+        <v>0.9361379850147004</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.06932498510276734</v>
+      </c>
+      <c r="W19">
+        <v>0.2553548064425408</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-0.3151135686489424</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1717992653100552</v>
+      </c>
+      <c r="C20">
+        <v>1041.143004761328</v>
+      </c>
+      <c r="D20">
+        <v>761.8470047613281</v>
+      </c>
+      <c r="E20">
+        <v>-759.396</v>
+      </c>
+      <c r="F20">
+        <v>278.604</v>
+      </c>
+      <c r="G20">
+        <v>557.9</v>
+      </c>
+      <c r="H20">
+        <v>509.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>121.5</v>
+      </c>
+      <c r="K20">
+        <v>141.3</v>
+      </c>
+      <c r="L20">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M20">
+        <v>66.53063520000001</v>
+      </c>
+      <c r="N20">
+        <v>-86.33063520000002</v>
+      </c>
+      <c r="O20">
+        <v>-18.992739744</v>
+      </c>
+      <c r="P20">
+        <v>-67.33789545600001</v>
+      </c>
+      <c r="Q20">
+        <v>73.962104544</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1536596929449064</v>
+      </c>
+      <c r="T20">
+        <v>0.9475543019051236</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.06547359704150249</v>
+      </c>
+      <c r="W20">
+        <v>0.2544350949735108</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-0.2976072592795569</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1737992653100553</v>
+      </c>
+      <c r="C21">
+        <v>1014.819335907061</v>
+      </c>
+      <c r="D21">
+        <v>751.0013359070612</v>
+      </c>
+      <c r="E21">
+        <v>-743.918</v>
+      </c>
+      <c r="F21">
+        <v>294.082</v>
+      </c>
+      <c r="G21">
+        <v>557.9</v>
+      </c>
+      <c r="H21">
+        <v>509.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>121.5</v>
+      </c>
+      <c r="K21">
+        <v>141.3</v>
+      </c>
+      <c r="L21">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M21">
+        <v>70.2267816</v>
+      </c>
+      <c r="N21">
+        <v>-90.02678160000001</v>
+      </c>
+      <c r="O21">
+        <v>-19.805891952</v>
+      </c>
+      <c r="P21">
+        <v>-70.22088964800001</v>
+      </c>
+      <c r="Q21">
+        <v>71.079110352</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1550777138454609</v>
+      </c>
+      <c r="T21">
+        <v>0.9592525031632115</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.06202761824984447</v>
+      </c>
+      <c r="W21">
+        <v>0.2536121952380629</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-0.281943719317475</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1757992653100552</v>
+      </c>
+      <c r="C22">
+        <v>988.8001310057034</v>
+      </c>
+      <c r="D22">
+        <v>740.4601310057033</v>
+      </c>
+      <c r="E22">
+        <v>-728.4400000000001</v>
+      </c>
+      <c r="F22">
+        <v>309.56</v>
+      </c>
+      <c r="G22">
+        <v>557.9</v>
+      </c>
+      <c r="H22">
+        <v>509.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>121.5</v>
+      </c>
+      <c r="K22">
+        <v>141.3</v>
+      </c>
+      <c r="L22">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M22">
+        <v>73.922928</v>
+      </c>
+      <c r="N22">
+        <v>-93.72292800000001</v>
+      </c>
+      <c r="O22">
+        <v>-20.61904416</v>
+      </c>
+      <c r="P22">
+        <v>-73.10388384000001</v>
+      </c>
+      <c r="Q22">
+        <v>68.19611616</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1565311852685291</v>
+      </c>
+      <c r="T22">
+        <v>0.9712431594527516</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.05892623733735226</v>
+      </c>
+      <c r="W22">
+        <v>0.2528715854761597</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-0.2678465333516011</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1777992653100552</v>
+      </c>
+      <c r="C23">
+        <v>963.0727469674439</v>
+      </c>
+      <c r="D23">
+        <v>730.2107469674438</v>
+      </c>
+      <c r="E23">
+        <v>-712.962</v>
+      </c>
+      <c r="F23">
+        <v>325.038</v>
+      </c>
+      <c r="G23">
+        <v>557.9</v>
+      </c>
+      <c r="H23">
+        <v>509.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>121.5</v>
+      </c>
+      <c r="K23">
+        <v>141.3</v>
+      </c>
+      <c r="L23">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M23">
+        <v>77.61907439999999</v>
+      </c>
+      <c r="N23">
+        <v>-97.4190744</v>
+      </c>
+      <c r="O23">
+        <v>-21.432196368</v>
+      </c>
+      <c r="P23">
+        <v>-75.98687803200001</v>
+      </c>
+      <c r="Q23">
+        <v>65.313121968</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1580214534364852</v>
+      </c>
+      <c r="T23">
+        <v>0.9835373766610142</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.05612022603557357</v>
+      </c>
+      <c r="W23">
+        <v>0.252201509977295</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-0.2550919365253346</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1797992653100552</v>
+      </c>
+      <c r="C24">
+        <v>937.6252311633243</v>
+      </c>
+      <c r="D24">
+        <v>720.2412311633243</v>
+      </c>
+      <c r="E24">
+        <v>-697.4839999999999</v>
+      </c>
+      <c r="F24">
+        <v>340.516</v>
+      </c>
+      <c r="G24">
+        <v>557.9</v>
+      </c>
+      <c r="H24">
+        <v>509.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>121.5</v>
+      </c>
+      <c r="K24">
+        <v>141.3</v>
+      </c>
+      <c r="L24">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M24">
+        <v>81.31522080000001</v>
+      </c>
+      <c r="N24">
+        <v>-101.1152208</v>
+      </c>
+      <c r="O24">
+        <v>-22.245348576</v>
+      </c>
+      <c r="P24">
+        <v>-78.86987222400002</v>
+      </c>
+      <c r="Q24">
+        <v>62.43012777599999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1595499336087478</v>
+      </c>
+      <c r="T24">
+        <v>0.9961468302079504</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.05356930667032022</v>
+      </c>
+      <c r="W24">
+        <v>0.2515923504328725</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-0.2434968485014555</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1817992653100552</v>
+      </c>
+      <c r="C25">
+        <v>912.4462749260227</v>
+      </c>
+      <c r="D25">
+        <v>710.5402749260228</v>
+      </c>
+      <c r="E25">
+        <v>-682.006</v>
+      </c>
+      <c r="F25">
+        <v>355.994</v>
+      </c>
+      <c r="G25">
+        <v>557.9</v>
+      </c>
+      <c r="H25">
+        <v>509.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>121.5</v>
+      </c>
+      <c r="K25">
+        <v>141.3</v>
+      </c>
+      <c r="L25">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M25">
+        <v>85.01136720000001</v>
+      </c>
+      <c r="N25">
+        <v>-104.8113672</v>
+      </c>
+      <c r="O25">
+        <v>-23.058500784</v>
+      </c>
+      <c r="P25">
+        <v>-81.75286641600002</v>
+      </c>
+      <c r="Q25">
+        <v>59.54713358399999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1611181145647056</v>
+      </c>
+      <c r="T25">
+        <v>1.009083802028833</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.0512402063803063</v>
+      </c>
+      <c r="W25">
+        <v>0.2510361612836172</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-0.2329100290013923</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1837992653100552</v>
+      </c>
+      <c r="C26">
+        <v>887.5251707584946</v>
+      </c>
+      <c r="D26">
+        <v>701.0971707584946</v>
+      </c>
+      <c r="E26">
+        <v>-666.528</v>
+      </c>
+      <c r="F26">
+        <v>371.472</v>
+      </c>
+      <c r="G26">
+        <v>557.9</v>
+      </c>
+      <c r="H26">
+        <v>509.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>121.5</v>
+      </c>
+      <c r="K26">
+        <v>141.3</v>
+      </c>
+      <c r="L26">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M26">
+        <v>88.7075136</v>
+      </c>
+      <c r="N26">
+        <v>-108.5075136</v>
+      </c>
+      <c r="O26">
+        <v>-23.871652992</v>
+      </c>
+      <c r="P26">
+        <v>-84.63586060800002</v>
+      </c>
+      <c r="Q26">
+        <v>56.664139392</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.162727563440557</v>
+      </c>
+      <c r="T26">
+        <v>1.022361220476581</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.04910519778112687</v>
+      </c>
+      <c r="W26">
+        <v>0.2505263212301331</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-0.2232054444596676</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1857992653100553</v>
+      </c>
+      <c r="C27">
+        <v>862.8517729100511</v>
+      </c>
+      <c r="D27">
+        <v>691.9017729100512</v>
+      </c>
+      <c r="E27">
+        <v>-651.05</v>
+      </c>
+      <c r="F27">
+        <v>386.95</v>
+      </c>
+      <c r="G27">
+        <v>557.9</v>
+      </c>
+      <c r="H27">
+        <v>509.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>121.5</v>
+      </c>
+      <c r="K27">
+        <v>141.3</v>
+      </c>
+      <c r="L27">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M27">
+        <v>92.40366</v>
+      </c>
+      <c r="N27">
+        <v>-112.20366</v>
+      </c>
+      <c r="O27">
+        <v>-24.6848052</v>
+      </c>
+      <c r="P27">
+        <v>-87.51885480000001</v>
+      </c>
+      <c r="Q27">
+        <v>53.7811452</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1643799309530977</v>
+      </c>
+      <c r="T27">
+        <v>1.035992703416268</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.0471409898698818</v>
+      </c>
+      <c r="W27">
+        <v>0.2500572683809278</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-0.2142772266812809</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1877992653100553</v>
+      </c>
+      <c r="C28">
+        <v>838.4164610147158</v>
+      </c>
+      <c r="D28">
+        <v>682.9444610147159</v>
+      </c>
+      <c r="E28">
+        <v>-635.572</v>
+      </c>
+      <c r="F28">
+        <v>402.428</v>
+      </c>
+      <c r="G28">
+        <v>557.9</v>
+      </c>
+      <c r="H28">
+        <v>509.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>121.5</v>
+      </c>
+      <c r="K28">
+        <v>141.3</v>
+      </c>
+      <c r="L28">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M28">
+        <v>96.09980640000001</v>
+      </c>
+      <c r="N28">
+        <v>-115.8998064</v>
+      </c>
+      <c r="O28">
+        <v>-25.497957408</v>
+      </c>
+      <c r="P28">
+        <v>-90.40184899200001</v>
+      </c>
+      <c r="Q28">
+        <v>50.898151008</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1660769570470585</v>
+      </c>
+      <c r="T28">
+        <v>1.049992604813786</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.04532787487488634</v>
+      </c>
+      <c r="W28">
+        <v>0.2496242965201229</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-0.2060357948858471</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1897992653100552</v>
+      </c>
+      <c r="C29">
+        <v>814.2101065178927</v>
+      </c>
+      <c r="D29">
+        <v>674.2161065178927</v>
+      </c>
+      <c r="E29">
+        <v>-620.0940000000001</v>
+      </c>
+      <c r="F29">
+        <v>417.906</v>
+      </c>
+      <c r="G29">
+        <v>557.9</v>
+      </c>
+      <c r="H29">
+        <v>509.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>121.5</v>
+      </c>
+      <c r="K29">
+        <v>141.3</v>
+      </c>
+      <c r="L29">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M29">
+        <v>99.79595280000001</v>
+      </c>
+      <c r="N29">
+        <v>-119.5959528</v>
+      </c>
+      <c r="O29">
+        <v>-26.311109616</v>
+      </c>
+      <c r="P29">
+        <v>-93.28484318400001</v>
+      </c>
+      <c r="Q29">
+        <v>48.015156816</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1678204770066072</v>
+      </c>
+      <c r="T29">
+        <v>1.0643760651537</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.043649064694335</v>
+      </c>
+      <c r="W29">
+        <v>0.2492233966490072</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-0.1984048395197044</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1917992653100553</v>
+      </c>
+      <c r="C30">
+        <v>790.2240416450468</v>
+      </c>
+      <c r="D30">
+        <v>665.7080416450469</v>
+      </c>
+      <c r="E30">
+        <v>-604.616</v>
+      </c>
+      <c r="F30">
+        <v>433.384</v>
+      </c>
+      <c r="G30">
+        <v>557.9</v>
+      </c>
+      <c r="H30">
+        <v>509.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>121.5</v>
+      </c>
+      <c r="K30">
+        <v>141.3</v>
+      </c>
+      <c r="L30">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M30">
+        <v>103.4920992</v>
+      </c>
+      <c r="N30">
+        <v>-123.2920992</v>
+      </c>
+      <c r="O30">
+        <v>-27.124261824</v>
+      </c>
+      <c r="P30">
+        <v>-96.16783737600002</v>
+      </c>
+      <c r="Q30">
+        <v>45.13216262399999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1696124280761435</v>
+      </c>
+      <c r="T30">
+        <v>1.079159066058613</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.04209016952668018</v>
+      </c>
+      <c r="W30">
+        <v>0.2488511324829712</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-0.1913189523940009</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1937992653100553</v>
+      </c>
+      <c r="C31">
+        <v>766.4500306906469</v>
+      </c>
+      <c r="D31">
+        <v>657.4120306906469</v>
+      </c>
+      <c r="E31">
+        <v>-589.138</v>
+      </c>
+      <c r="F31">
+        <v>448.862</v>
+      </c>
+      <c r="G31">
+        <v>557.9</v>
+      </c>
+      <c r="H31">
+        <v>509.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>121.5</v>
+      </c>
+      <c r="K31">
+        <v>141.3</v>
+      </c>
+      <c r="L31">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M31">
+        <v>107.1882456</v>
+      </c>
+      <c r="N31">
+        <v>-126.9882456</v>
+      </c>
+      <c r="O31">
+        <v>-27.937414032</v>
+      </c>
+      <c r="P31">
+        <v>-99.05083156800001</v>
+      </c>
+      <c r="Q31">
+        <v>42.249168432</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1714548566405962</v>
+      </c>
+      <c r="T31">
+        <v>1.094358489524227</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.04063878437058775</v>
+      </c>
+      <c r="W31">
+        <v>0.2485045417076964</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-0.1847217471390352</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1957992653100552</v>
+      </c>
+      <c r="C32">
+        <v>742.8802434274551</v>
+      </c>
+      <c r="D32">
+        <v>649.3202434274551</v>
+      </c>
+      <c r="E32">
+        <v>-573.6600000000001</v>
+      </c>
+      <c r="F32">
+        <v>464.34</v>
+      </c>
+      <c r="G32">
+        <v>557.9</v>
+      </c>
+      <c r="H32">
+        <v>509.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>121.5</v>
+      </c>
+      <c r="K32">
+        <v>141.3</v>
+      </c>
+      <c r="L32">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M32">
+        <v>110.884392</v>
+      </c>
+      <c r="N32">
+        <v>-130.684392</v>
+      </c>
+      <c r="O32">
+        <v>-28.75056624</v>
+      </c>
+      <c r="P32">
+        <v>-101.93382576</v>
+      </c>
+      <c r="Q32">
+        <v>39.36617424000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1733499260211761</v>
+      </c>
+      <c r="T32">
+        <v>1.109992182231716</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.03928415822490149</v>
+      </c>
+      <c r="W32">
+        <v>0.2481810569841065</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-0.1785643555677339</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1977992653100553</v>
+      </c>
+      <c r="C33">
+        <v>719.5072304556986</v>
+      </c>
+      <c r="D33">
+        <v>641.4252304556986</v>
+      </c>
+      <c r="E33">
+        <v>-558.182</v>
+      </c>
+      <c r="F33">
+        <v>479.818</v>
+      </c>
+      <c r="G33">
+        <v>557.9</v>
+      </c>
+      <c r="H33">
+        <v>509.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>121.5</v>
+      </c>
+      <c r="K33">
+        <v>141.3</v>
+      </c>
+      <c r="L33">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M33">
+        <v>114.5805384</v>
+      </c>
+      <c r="N33">
+        <v>-134.3805384</v>
+      </c>
+      <c r="O33">
+        <v>-29.563718448</v>
+      </c>
+      <c r="P33">
+        <v>-104.816819952</v>
+      </c>
+      <c r="Q33">
+        <v>36.48318004799998</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1752999249490193</v>
+      </c>
+      <c r="T33">
+        <v>1.126079025452466</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.03801692731442081</v>
+      </c>
+      <c r="W33">
+        <v>0.2478784422426837</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-0.1728042150655493</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1997992653100552</v>
+      </c>
+      <c r="C34">
+        <v>696.3239003289989</v>
+      </c>
+      <c r="D34">
+        <v>633.719900328999</v>
+      </c>
+      <c r="E34">
+        <v>-542.704</v>
+      </c>
+      <c r="F34">
+        <v>495.296</v>
+      </c>
+      <c r="G34">
+        <v>557.9</v>
+      </c>
+      <c r="H34">
+        <v>509.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>121.5</v>
+      </c>
+      <c r="K34">
+        <v>141.3</v>
+      </c>
+      <c r="L34">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M34">
+        <v>118.2766848</v>
+      </c>
+      <c r="N34">
+        <v>-138.0766848</v>
+      </c>
+      <c r="O34">
+        <v>-30.376870656</v>
+      </c>
+      <c r="P34">
+        <v>-107.699814144</v>
+      </c>
+      <c r="Q34">
+        <v>33.600185856</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1773072767865048</v>
+      </c>
+      <c r="T34">
+        <v>1.142639011120884</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.03682889833584516</v>
+      </c>
+      <c r="W34">
+        <v>0.2475947409225998</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-0.1674040833447508</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2017992653100553</v>
+      </c>
+      <c r="C35">
+        <v>673.3234983094218</v>
+      </c>
+      <c r="D35">
+        <v>626.1974983094218</v>
+      </c>
+      <c r="E35">
+        <v>-527.226</v>
+      </c>
+      <c r="F35">
+        <v>510.774</v>
+      </c>
+      <c r="G35">
+        <v>557.9</v>
+      </c>
+      <c r="H35">
+        <v>509.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>121.5</v>
+      </c>
+      <c r="K35">
+        <v>141.3</v>
+      </c>
+      <c r="L35">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M35">
+        <v>121.9728312</v>
+      </c>
+      <c r="N35">
+        <v>-141.7728312</v>
+      </c>
+      <c r="O35">
+        <v>-31.190022864</v>
+      </c>
+      <c r="P35">
+        <v>-110.582808336</v>
+      </c>
+      <c r="Q35">
+        <v>30.717191664</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1793745495743631</v>
+      </c>
+      <c r="T35">
+        <v>1.159693324719703</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.03571287111354682</v>
+      </c>
+      <c r="W35">
+        <v>0.247328233621915</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-0.1623312323343038</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2037992653100552</v>
+      </c>
+      <c r="C36">
+        <v>650.499586617875</v>
+      </c>
+      <c r="D36">
+        <v>618.8515866178752</v>
+      </c>
+      <c r="E36">
+        <v>-511.7479999999999</v>
+      </c>
+      <c r="F36">
+        <v>526.2520000000001</v>
+      </c>
+      <c r="G36">
+        <v>557.9</v>
+      </c>
+      <c r="H36">
+        <v>509.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>121.5</v>
+      </c>
+      <c r="K36">
+        <v>141.3</v>
+      </c>
+      <c r="L36">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M36">
+        <v>125.6689776</v>
+      </c>
+      <c r="N36">
+        <v>-145.4689776</v>
+      </c>
+      <c r="O36">
+        <v>-32.003175072</v>
+      </c>
+      <c r="P36">
+        <v>-113.465802528</v>
+      </c>
+      <c r="Q36">
+        <v>27.834197472</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1815044669921565</v>
+      </c>
+      <c r="T36">
+        <v>1.177264435700305</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.03466249255138367</v>
+      </c>
+      <c r="W36">
+        <v>0.2470774032212704</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-0.1575567843244712</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2057992653100552</v>
+      </c>
+      <c r="C37">
+        <v>627.8460260584784</v>
+      </c>
+      <c r="D37">
+        <v>611.6760260584784</v>
+      </c>
+      <c r="E37">
+        <v>-496.27</v>
+      </c>
+      <c r="F37">
+        <v>541.73</v>
+      </c>
+      <c r="G37">
+        <v>557.9</v>
+      </c>
+      <c r="H37">
+        <v>509.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>121.5</v>
+      </c>
+      <c r="K37">
+        <v>141.3</v>
+      </c>
+      <c r="L37">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M37">
+        <v>129.365124</v>
+      </c>
+      <c r="N37">
+        <v>-149.165124</v>
+      </c>
+      <c r="O37">
+        <v>-32.81632728</v>
+      </c>
+      <c r="P37">
+        <v>-116.34879672</v>
+      </c>
+      <c r="Q37">
+        <v>24.95120327999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1836999203304974</v>
+      </c>
+      <c r="T37">
+        <v>1.19537619624954</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.03367213562134414</v>
+      </c>
+      <c r="W37">
+        <v>0.246840905986377</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-0.1530551619152007</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2077992653100552</v>
+      </c>
+      <c r="C38">
+        <v>605.356958906672</v>
+      </c>
+      <c r="D38">
+        <v>604.664958906672</v>
+      </c>
+      <c r="E38">
+        <v>-480.792</v>
+      </c>
+      <c r="F38">
+        <v>557.208</v>
+      </c>
+      <c r="G38">
+        <v>557.9</v>
+      </c>
+      <c r="H38">
+        <v>509.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>121.5</v>
+      </c>
+      <c r="K38">
+        <v>141.3</v>
+      </c>
+      <c r="L38">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M38">
+        <v>133.0612704</v>
+      </c>
+      <c r="N38">
+        <v>-152.8612704</v>
+      </c>
+      <c r="O38">
+        <v>-33.629479488</v>
+      </c>
+      <c r="P38">
+        <v>-119.231790912</v>
+      </c>
+      <c r="Q38">
+        <v>22.06820908799999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1859639815856614</v>
+      </c>
+      <c r="T38">
+        <v>1.214053949315939</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.03273679852075125</v>
+      </c>
+      <c r="W38">
+        <v>0.2466175474867554</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-0.1488036296397783</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2097992653100553</v>
+      </c>
+      <c r="C39">
+        <v>583.0267929608112</v>
+      </c>
+      <c r="D39">
+        <v>597.8127929608112</v>
+      </c>
+      <c r="E39">
+        <v>-465.3140000000001</v>
+      </c>
+      <c r="F39">
+        <v>572.6859999999999</v>
+      </c>
+      <c r="G39">
+        <v>557.9</v>
+      </c>
+      <c r="H39">
+        <v>509.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>121.5</v>
+      </c>
+      <c r="K39">
+        <v>141.3</v>
+      </c>
+      <c r="L39">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M39">
+        <v>136.7574168</v>
+      </c>
+      <c r="N39">
+        <v>-156.5574168</v>
+      </c>
+      <c r="O39">
+        <v>-34.44263169599999</v>
+      </c>
+      <c r="P39">
+        <v>-122.114785104</v>
+      </c>
+      <c r="Q39">
+        <v>19.18521489600001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1882999178013068</v>
+      </c>
+      <c r="T39">
+        <v>1.233324646924129</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.03185202018235257</v>
+      </c>
+      <c r="W39">
+        <v>0.2464062624195458</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-0.1447819099197845</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2117992653100552</v>
+      </c>
+      <c r="C40">
+        <v>560.8501866659938</v>
+      </c>
+      <c r="D40">
+        <v>591.1141866659939</v>
+      </c>
+      <c r="E40">
+        <v>-449.836</v>
+      </c>
+      <c r="F40">
+        <v>588.164</v>
+      </c>
+      <c r="G40">
+        <v>557.9</v>
+      </c>
+      <c r="H40">
+        <v>509.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>121.5</v>
+      </c>
+      <c r="K40">
+        <v>141.3</v>
+      </c>
+      <c r="L40">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M40">
+        <v>140.4535632</v>
+      </c>
+      <c r="N40">
+        <v>-160.2535632</v>
+      </c>
+      <c r="O40">
+        <v>-35.255783904</v>
+      </c>
+      <c r="P40">
+        <v>-124.997779296</v>
+      </c>
+      <c r="Q40">
+        <v>16.30222070400001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1907112067981021</v>
+      </c>
+      <c r="T40">
+        <v>1.253216979939034</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.03101380912492224</v>
+      </c>
+      <c r="W40">
+        <v>0.2462060976190314</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.1409718596587375</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2137992653100552</v>
+      </c>
+      <c r="C41">
+        <v>538.8220352269429</v>
+      </c>
+      <c r="D41">
+        <v>584.5640352269431</v>
+      </c>
+      <c r="E41">
+        <v>-434.3579999999999</v>
+      </c>
+      <c r="F41">
+        <v>603.6420000000001</v>
+      </c>
+      <c r="G41">
+        <v>557.9</v>
+      </c>
+      <c r="H41">
+        <v>509.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>121.5</v>
+      </c>
+      <c r="K41">
+        <v>141.3</v>
+      </c>
+      <c r="L41">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M41">
+        <v>144.1497096</v>
+      </c>
+      <c r="N41">
+        <v>-163.9497096</v>
+      </c>
+      <c r="O41">
+        <v>-36.068936112</v>
+      </c>
+      <c r="P41">
+        <v>-127.880773488</v>
+      </c>
+      <c r="Q41">
+        <v>13.41922651199998</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.19320155445053</v>
+      </c>
+      <c r="T41">
+        <v>1.273761520593773</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.03021858324992422</v>
+      </c>
+      <c r="W41">
+        <v>0.2460161976800819</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.1373571965905647</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2157992653100552</v>
+      </c>
+      <c r="C42">
+        <v>516.9374576340768</v>
+      </c>
+      <c r="D42">
+        <v>578.1574576340769</v>
+      </c>
+      <c r="E42">
+        <v>-418.88</v>
+      </c>
+      <c r="F42">
+        <v>619.12</v>
+      </c>
+      <c r="G42">
+        <v>557.9</v>
+      </c>
+      <c r="H42">
+        <v>509.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>121.5</v>
+      </c>
+      <c r="K42">
+        <v>141.3</v>
+      </c>
+      <c r="L42">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M42">
+        <v>147.845856</v>
+      </c>
+      <c r="N42">
+        <v>-167.645856</v>
+      </c>
+      <c r="O42">
+        <v>-36.88208831999999</v>
+      </c>
+      <c r="P42">
+        <v>-130.76376768</v>
+      </c>
+      <c r="Q42">
+        <v>10.53623232000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1957749136913721</v>
+      </c>
+      <c r="T42">
+        <v>1.294990879270336</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.02946311866867613</v>
+      </c>
+      <c r="W42">
+        <v>0.2458357927380799</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.1339232666758006</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2177992653100552</v>
+      </c>
+      <c r="C43">
+        <v>495.191784533458</v>
+      </c>
+      <c r="D43">
+        <v>571.8897845334581</v>
+      </c>
+      <c r="E43">
+        <v>-403.4019999999999</v>
+      </c>
+      <c r="F43">
+        <v>634.5980000000001</v>
+      </c>
+      <c r="G43">
+        <v>557.9</v>
+      </c>
+      <c r="H43">
+        <v>509.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>121.5</v>
+      </c>
+      <c r="K43">
+        <v>141.3</v>
+      </c>
+      <c r="L43">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M43">
+        <v>151.5420024</v>
+      </c>
+      <c r="N43">
+        <v>-171.3420024</v>
+      </c>
+      <c r="O43">
+        <v>-37.69524052800001</v>
+      </c>
+      <c r="P43">
+        <v>-133.646761872</v>
+      </c>
+      <c r="Q43">
+        <v>7.65323812799997</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1984355054488531</v>
+      </c>
+      <c r="T43">
+        <v>1.31693987722407</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.02874450601822061</v>
+      </c>
+      <c r="W43">
+        <v>0.2456641880371511</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.1306568455373665</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2197992653100553</v>
+      </c>
+      <c r="C44">
+        <v>473.5805468772795</v>
+      </c>
+      <c r="D44">
+        <v>565.7565468772794</v>
+      </c>
+      <c r="E44">
+        <v>-387.9240000000001</v>
+      </c>
+      <c r="F44">
+        <v>650.0759999999999</v>
+      </c>
+      <c r="G44">
+        <v>557.9</v>
+      </c>
+      <c r="H44">
+        <v>509.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>121.5</v>
+      </c>
+      <c r="K44">
+        <v>141.3</v>
+      </c>
+      <c r="L44">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M44">
+        <v>155.2381488</v>
+      </c>
+      <c r="N44">
+        <v>-175.0381488</v>
+      </c>
+      <c r="O44">
+        <v>-38.50839273599999</v>
+      </c>
+      <c r="P44">
+        <v>-136.529756064</v>
+      </c>
+      <c r="Q44">
+        <v>4.770243936000014</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2011878417496953</v>
+      </c>
+      <c r="T44">
+        <v>1.339645737176209</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.02806011301778679</v>
+      </c>
+      <c r="W44">
+        <v>0.2455007549886475</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.1275459682626672</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2217992653100552</v>
+      </c>
+      <c r="C45">
+        <v>452.0994652969081</v>
+      </c>
+      <c r="D45">
+        <v>559.7534652969082</v>
+      </c>
+      <c r="E45">
+        <v>-372.446</v>
+      </c>
+      <c r="F45">
+        <v>665.554</v>
+      </c>
+      <c r="G45">
+        <v>557.9</v>
+      </c>
+      <c r="H45">
+        <v>509.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>121.5</v>
+      </c>
+      <c r="K45">
+        <v>141.3</v>
+      </c>
+      <c r="L45">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M45">
+        <v>158.9342952</v>
+      </c>
+      <c r="N45">
+        <v>-178.7342952</v>
+      </c>
+      <c r="O45">
+        <v>-39.321544944</v>
+      </c>
+      <c r="P45">
+        <v>-139.412750256</v>
+      </c>
+      <c r="Q45">
+        <v>1.887249744000002</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2040367512540759</v>
+      </c>
+      <c r="T45">
+        <v>1.363148293968774</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.02740755224993128</v>
+      </c>
+      <c r="W45">
+        <v>0.2453449234772836</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.124579782954233</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2237992653100553</v>
+      </c>
+      <c r="C46">
+        <v>430.7444401453816</v>
+      </c>
+      <c r="D46">
+        <v>553.8764401453817</v>
+      </c>
+      <c r="E46">
+        <v>-356.968</v>
+      </c>
+      <c r="F46">
+        <v>681.032</v>
+      </c>
+      <c r="G46">
+        <v>557.9</v>
+      </c>
+      <c r="H46">
+        <v>509.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>121.5</v>
+      </c>
+      <c r="K46">
+        <v>141.3</v>
+      </c>
+      <c r="L46">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M46">
+        <v>162.6304416</v>
+      </c>
+      <c r="N46">
+        <v>-182.4304416</v>
+      </c>
+      <c r="O46">
+        <v>-40.134697152</v>
+      </c>
+      <c r="P46">
+        <v>-142.295744448</v>
+      </c>
+      <c r="Q46">
+        <v>-0.9957444480000106</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2069874075264702</v>
+      </c>
+      <c r="T46">
+        <v>1.387490227789645</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.02678465333516011</v>
+      </c>
+      <c r="W46">
+        <v>0.2451961752164362</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.1217484242507278</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2257992653100553</v>
+      </c>
+      <c r="C47">
+        <v>409.5115421606715</v>
+      </c>
+      <c r="D47">
+        <v>548.1215421606715</v>
+      </c>
+      <c r="E47">
+        <v>-341.49</v>
+      </c>
+      <c r="F47">
+        <v>696.51</v>
+      </c>
+      <c r="G47">
+        <v>557.9</v>
+      </c>
+      <c r="H47">
+        <v>509.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>121.5</v>
+      </c>
+      <c r="K47">
+        <v>141.3</v>
+      </c>
+      <c r="L47">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M47">
+        <v>166.326588</v>
+      </c>
+      <c r="N47">
+        <v>-186.126588</v>
+      </c>
+      <c r="O47">
+        <v>-40.94784936</v>
+      </c>
+      <c r="P47">
+        <v>-145.17873864</v>
+      </c>
+      <c r="Q47">
+        <v>-3.878738640000023</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2100453603905878</v>
+      </c>
+      <c r="T47">
+        <v>1.412717322840366</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.026189438816601</v>
+      </c>
+      <c r="W47">
+        <v>0.2450540379894043</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.1190429037118228</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2277992653100552</v>
+      </c>
+      <c r="C48">
+        <v>388.3970037050224</v>
+      </c>
+      <c r="D48">
+        <v>542.4850037050226</v>
+      </c>
+      <c r="E48">
+        <v>-326.0119999999999</v>
+      </c>
+      <c r="F48">
+        <v>711.9880000000001</v>
+      </c>
+      <c r="G48">
+        <v>557.9</v>
+      </c>
+      <c r="H48">
+        <v>509.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>121.5</v>
+      </c>
+      <c r="K48">
+        <v>141.3</v>
+      </c>
+      <c r="L48">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M48">
+        <v>170.0227344</v>
+      </c>
+      <c r="N48">
+        <v>-189.8227344</v>
+      </c>
+      <c r="O48">
+        <v>-41.761001568</v>
+      </c>
+      <c r="P48">
+        <v>-148.061732832</v>
+      </c>
+      <c r="Q48">
+        <v>-6.761732832000007</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2132165707681913</v>
+      </c>
+      <c r="T48">
+        <v>1.438878754744817</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.02562010319015315</v>
+      </c>
+      <c r="W48">
+        <v>0.2449180806418086</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.1164550145006962</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2297992653100553</v>
+      </c>
+      <c r="C49">
+        <v>367.397210539326</v>
+      </c>
+      <c r="D49">
+        <v>536.963210539326</v>
+      </c>
+      <c r="E49">
+        <v>-310.534</v>
+      </c>
+      <c r="F49">
+        <v>727.466</v>
+      </c>
+      <c r="G49">
+        <v>557.9</v>
+      </c>
+      <c r="H49">
+        <v>509.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>121.5</v>
+      </c>
+      <c r="K49">
+        <v>141.3</v>
+      </c>
+      <c r="L49">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M49">
+        <v>173.7188808</v>
+      </c>
+      <c r="N49">
+        <v>-193.5188808</v>
+      </c>
+      <c r="O49">
+        <v>-42.574153776</v>
+      </c>
+      <c r="P49">
+        <v>-150.944727024</v>
+      </c>
+      <c r="Q49">
+        <v>-9.644727024000019</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2165074494619308</v>
+      </c>
+      <c r="T49">
+        <v>1.46602741049472</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.02507499461163925</v>
+      </c>
+      <c r="W49">
+        <v>0.2447879087132595</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.1139772482347239</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2317992653100552</v>
+      </c>
+      <c r="C50">
+        <v>346.5086940947904</v>
+      </c>
+      <c r="D50">
+        <v>531.5526940947905</v>
+      </c>
+      <c r="E50">
+        <v>-295.056</v>
+      </c>
+      <c r="F50">
+        <v>742.944</v>
+      </c>
+      <c r="G50">
+        <v>557.9</v>
+      </c>
+      <c r="H50">
+        <v>509.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>121.5</v>
+      </c>
+      <c r="K50">
+        <v>141.3</v>
+      </c>
+      <c r="L50">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M50">
+        <v>177.4150272</v>
+      </c>
+      <c r="N50">
+        <v>-197.2150272</v>
+      </c>
+      <c r="O50">
+        <v>-43.38730598399999</v>
+      </c>
+      <c r="P50">
+        <v>-153.827721216</v>
+      </c>
+      <c r="Q50">
+        <v>-12.527721216</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2199249004131217</v>
+      </c>
+      <c r="T50">
+        <v>1.494220245311926</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.02455259889056344</v>
+      </c>
+      <c r="W50">
+        <v>0.2446631606150666</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.1116027222298339</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2337992653100552</v>
+      </c>
+      <c r="C51">
+        <v>325.7281242071773</v>
+      </c>
+      <c r="D51">
+        <v>526.2501242071772</v>
+      </c>
+      <c r="E51">
+        <v>-279.5780000000001</v>
+      </c>
+      <c r="F51">
+        <v>758.4219999999999</v>
+      </c>
+      <c r="G51">
+        <v>557.9</v>
+      </c>
+      <c r="H51">
+        <v>509.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>121.5</v>
+      </c>
+      <c r="K51">
+        <v>141.3</v>
+      </c>
+      <c r="L51">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M51">
+        <v>181.1111736</v>
+      </c>
+      <c r="N51">
+        <v>-200.9111736</v>
+      </c>
+      <c r="O51">
+        <v>-44.200458192</v>
+      </c>
+      <c r="P51">
+        <v>-156.710715408</v>
+      </c>
+      <c r="Q51">
+        <v>-15.41071540799999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2234763690486731</v>
+      </c>
+      <c r="T51">
+        <v>1.523518681494512</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.02405152544381724</v>
+      </c>
+      <c r="W51">
+        <v>0.2445435042759836</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.1093251156537147</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2357992653100552</v>
+      </c>
+      <c r="C52">
+        <v>305.0523022816288</v>
+      </c>
+      <c r="D52">
+        <v>521.052302281629</v>
+      </c>
+      <c r="E52">
+        <v>-264.1</v>
+      </c>
+      <c r="F52">
+        <v>773.9</v>
+      </c>
+      <c r="G52">
+        <v>557.9</v>
+      </c>
+      <c r="H52">
+        <v>509.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>121.5</v>
+      </c>
+      <c r="K52">
+        <v>141.3</v>
+      </c>
+      <c r="L52">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M52">
+        <v>184.80732</v>
+      </c>
+      <c r="N52">
+        <v>-204.60732</v>
+      </c>
+      <c r="O52">
+        <v>-45.0136104</v>
+      </c>
+      <c r="P52">
+        <v>-159.5937096</v>
+      </c>
+      <c r="Q52">
+        <v>-18.2937096</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2271698964296466</v>
+      </c>
+      <c r="T52">
+        <v>1.553989055124403</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.0235704949349409</v>
+      </c>
+      <c r="W52">
+        <v>0.2444286341904639</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.1071386133406405</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2377992653100552</v>
+      </c>
+      <c r="C53">
+        <v>284.478154858603</v>
+      </c>
+      <c r="D53">
+        <v>515.956154858603</v>
+      </c>
+      <c r="E53">
+        <v>-248.622</v>
+      </c>
+      <c r="F53">
+        <v>789.378</v>
+      </c>
+      <c r="G53">
+        <v>557.9</v>
+      </c>
+      <c r="H53">
+        <v>509.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>121.5</v>
+      </c>
+      <c r="K53">
+        <v>141.3</v>
+      </c>
+      <c r="L53">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M53">
+        <v>188.5034664</v>
+      </c>
+      <c r="N53">
+        <v>-208.3034664</v>
+      </c>
+      <c r="O53">
+        <v>-45.826762608</v>
+      </c>
+      <c r="P53">
+        <v>-162.476703792</v>
+      </c>
+      <c r="Q53">
+        <v>-21.17670379200001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2310141800302516</v>
+      </c>
+      <c r="T53">
+        <v>1.58570311747388</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.02310832836758912</v>
+      </c>
+      <c r="W53">
+        <v>0.2443182688141803</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.1050378562163141</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2397992653100552</v>
+      </c>
+      <c r="C54">
+        <v>264.0027275537175</v>
+      </c>
+      <c r="D54">
+        <v>510.9587275537176</v>
+      </c>
+      <c r="E54">
+        <v>-233.144</v>
+      </c>
+      <c r="F54">
+        <v>804.856</v>
+      </c>
+      <c r="G54">
+        <v>557.9</v>
+      </c>
+      <c r="H54">
+        <v>509.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>121.5</v>
+      </c>
+      <c r="K54">
+        <v>141.3</v>
+      </c>
+      <c r="L54">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M54">
+        <v>192.1996128</v>
+      </c>
+      <c r="N54">
+        <v>-211.9996128</v>
+      </c>
+      <c r="O54">
+        <v>-46.639914816</v>
+      </c>
+      <c r="P54">
+        <v>-165.359697984</v>
+      </c>
+      <c r="Q54">
+        <v>-24.05969798400002</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2350186421142152</v>
+      </c>
+      <c r="T54">
+        <v>1.618738599087919</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.02266393743744317</v>
+      </c>
+      <c r="W54">
+        <v>0.2442121482600614</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.1030178974429234</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2417992653100553</v>
+      </c>
+      <c r="C55">
+        <v>243.6231793464051</v>
+      </c>
+      <c r="D55">
+        <v>506.0571793464052</v>
+      </c>
+      <c r="E55">
+        <v>-217.6659999999999</v>
+      </c>
+      <c r="F55">
+        <v>820.3340000000001</v>
+      </c>
+      <c r="G55">
+        <v>557.9</v>
+      </c>
+      <c r="H55">
+        <v>509.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>121.5</v>
+      </c>
+      <c r="K55">
+        <v>141.3</v>
+      </c>
+      <c r="L55">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M55">
+        <v>195.8957592</v>
+      </c>
+      <c r="N55">
+        <v>-215.6957592</v>
+      </c>
+      <c r="O55">
+        <v>-47.453067024</v>
+      </c>
+      <c r="P55">
+        <v>-168.242692176</v>
+      </c>
+      <c r="Q55">
+        <v>-26.94269217600001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2391935068400496</v>
+      </c>
+      <c r="T55">
+        <v>1.653179845877024</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.02223631597635934</v>
+      </c>
+      <c r="W55">
+        <v>0.2441100322551547</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.1010741635289061</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2437992653100552</v>
+      </c>
+      <c r="C56">
+        <v>223.3367771941681</v>
+      </c>
+      <c r="D56">
+        <v>501.2487771941682</v>
+      </c>
+      <c r="E56">
+        <v>-202.188</v>
+      </c>
+      <c r="F56">
+        <v>835.812</v>
+      </c>
+      <c r="G56">
+        <v>557.9</v>
+      </c>
+      <c r="H56">
+        <v>509.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>121.5</v>
+      </c>
+      <c r="K56">
+        <v>141.3</v>
+      </c>
+      <c r="L56">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M56">
+        <v>199.5919056</v>
+      </c>
+      <c r="N56">
+        <v>-219.3919056</v>
+      </c>
+      <c r="O56">
+        <v>-48.266219232</v>
+      </c>
+      <c r="P56">
+        <v>-171.125686368</v>
+      </c>
+      <c r="Q56">
+        <v>-29.82568636800002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2435498874235289</v>
+      </c>
+      <c r="T56">
+        <v>1.689118538178698</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.0218245323471675</v>
+      </c>
+      <c r="W56">
+        <v>0.2440116983245036</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.09920241975985222</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2457992653100552</v>
+      </c>
+      <c r="C57">
+        <v>203.1408909509881</v>
+      </c>
+      <c r="D57">
+        <v>496.5308909509882</v>
+      </c>
+      <c r="E57">
+        <v>-186.7099999999999</v>
+      </c>
+      <c r="F57">
+        <v>851.2900000000001</v>
+      </c>
+      <c r="G57">
+        <v>557.9</v>
+      </c>
+      <c r="H57">
+        <v>509.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>121.5</v>
+      </c>
+      <c r="K57">
+        <v>141.3</v>
+      </c>
+      <c r="L57">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M57">
+        <v>203.288052</v>
+      </c>
+      <c r="N57">
+        <v>-223.088052</v>
+      </c>
+      <c r="O57">
+        <v>-49.07937144</v>
+      </c>
+      <c r="P57">
+        <v>-174.00868056</v>
+      </c>
+      <c r="Q57">
+        <v>-32.70868056</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2480998849218296</v>
+      </c>
+      <c r="T57">
+        <v>1.726654505693781</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.02142772266812809</v>
+      </c>
+      <c r="W57">
+        <v>0.243916940173149</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.09739873940058219</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2477992653100552</v>
+      </c>
+      <c r="C58">
+        <v>183.0329885700348</v>
+      </c>
+      <c r="D58">
+        <v>491.9009885700348</v>
+      </c>
+      <c r="E58">
+        <v>-171.232</v>
+      </c>
+      <c r="F58">
+        <v>866.768</v>
+      </c>
+      <c r="G58">
+        <v>557.9</v>
+      </c>
+      <c r="H58">
+        <v>509.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>121.5</v>
+      </c>
+      <c r="K58">
+        <v>141.3</v>
+      </c>
+      <c r="L58">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M58">
+        <v>206.9841984</v>
+      </c>
+      <c r="N58">
+        <v>-226.7841984</v>
+      </c>
+      <c r="O58">
+        <v>-49.892523648</v>
+      </c>
+      <c r="P58">
+        <v>-176.891674752</v>
+      </c>
+      <c r="Q58">
+        <v>-35.59167475200002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2528567004882347</v>
+      </c>
+      <c r="T58">
+        <v>1.765896653550457</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.02104508476334009</v>
+      </c>
+      <c r="W58">
+        <v>0.2438255662414856</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.09565947619700044</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2497992653100553</v>
+      </c>
+      <c r="C59">
+        <v>163.0106315722892</v>
+      </c>
+      <c r="D59">
+        <v>487.3566315722893</v>
+      </c>
+      <c r="E59">
+        <v>-155.7539999999999</v>
+      </c>
+      <c r="F59">
+        <v>882.2460000000001</v>
+      </c>
+      <c r="G59">
+        <v>557.9</v>
+      </c>
+      <c r="H59">
+        <v>509.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>121.5</v>
+      </c>
+      <c r="K59">
+        <v>141.3</v>
+      </c>
+      <c r="L59">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M59">
+        <v>210.6803448</v>
+      </c>
+      <c r="N59">
+        <v>-230.4803448</v>
+      </c>
+      <c r="O59">
+        <v>-50.705675856</v>
+      </c>
+      <c r="P59">
+        <v>-179.774668944</v>
+      </c>
+      <c r="Q59">
+        <v>-38.47466894400003</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2578347632902868</v>
+      </c>
+      <c r="T59">
+        <v>1.806964017586515</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.02067587274994815</v>
+      </c>
+      <c r="W59">
+        <v>0.2437373984126876</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.09398123977249173</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2517992653100553</v>
+      </c>
+      <c r="C60">
+        <v>143.0714707640429</v>
+      </c>
+      <c r="D60">
+        <v>482.895470764043</v>
+      </c>
+      <c r="E60">
+        <v>-140.2760000000001</v>
+      </c>
+      <c r="F60">
+        <v>897.7239999999999</v>
+      </c>
+      <c r="G60">
+        <v>557.9</v>
+      </c>
+      <c r="H60">
+        <v>509.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>121.5</v>
+      </c>
+      <c r="K60">
+        <v>141.3</v>
+      </c>
+      <c r="L60">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M60">
+        <v>214.3764912</v>
+      </c>
+      <c r="N60">
+        <v>-234.1764912</v>
+      </c>
+      <c r="O60">
+        <v>-51.518828064</v>
+      </c>
+      <c r="P60">
+        <v>-182.657663136</v>
+      </c>
+      <c r="Q60">
+        <v>-41.35766313600001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2630498767019602</v>
+      </c>
+      <c r="T60">
+        <v>1.849986970386194</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.02031939218529388</v>
+      </c>
+      <c r="W60">
+        <v>0.2436522708538482</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.09236087356951761</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2537992653100552</v>
+      </c>
+      <c r="C61">
+        <v>123.2132421874707</v>
+      </c>
+      <c r="D61">
+        <v>478.5152421874705</v>
+      </c>
+      <c r="E61">
+        <v>-124.7980000000001</v>
+      </c>
+      <c r="F61">
+        <v>913.2019999999999</v>
+      </c>
+      <c r="G61">
+        <v>557.9</v>
+      </c>
+      <c r="H61">
+        <v>509.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>121.5</v>
+      </c>
+      <c r="K61">
+        <v>141.3</v>
+      </c>
+      <c r="L61">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M61">
+        <v>218.0726376</v>
+      </c>
+      <c r="N61">
+        <v>-237.8726376</v>
+      </c>
+      <c r="O61">
+        <v>-52.33198027199999</v>
+      </c>
+      <c r="P61">
+        <v>-185.540657328</v>
+      </c>
+      <c r="Q61">
+        <v>-44.240657328</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2685193858898128</v>
+      </c>
+      <c r="T61">
+        <v>1.895108603810247</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.01997499570757704</v>
+      </c>
+      <c r="W61">
+        <v>0.2435700289749694</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.0907954350344411</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2557992653100552</v>
+      </c>
+      <c r="C62">
+        <v>103.4337632896071</v>
+      </c>
+      <c r="D62">
+        <v>474.2137632896072</v>
+      </c>
+      <c r="E62">
+        <v>-109.3200000000001</v>
+      </c>
+      <c r="F62">
+        <v>928.6799999999999</v>
+      </c>
+      <c r="G62">
+        <v>557.9</v>
+      </c>
+      <c r="H62">
+        <v>509.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>121.5</v>
+      </c>
+      <c r="K62">
+        <v>141.3</v>
+      </c>
+      <c r="L62">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M62">
+        <v>221.768784</v>
+      </c>
+      <c r="N62">
+        <v>-241.568784</v>
+      </c>
+      <c r="O62">
+        <v>-53.14513248</v>
+      </c>
+      <c r="P62">
+        <v>-188.42365152</v>
+      </c>
+      <c r="Q62">
+        <v>-47.12365152000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2742623705370582</v>
+      </c>
+      <c r="T62">
+        <v>1.942486318905503</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.01964207911245075</v>
+      </c>
+      <c r="W62">
+        <v>0.2434905284920532</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.08928217778386704</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2577992653100553</v>
+      </c>
+      <c r="C63">
+        <v>83.73092929611767</v>
+      </c>
+      <c r="D63">
+        <v>469.9889292961175</v>
+      </c>
+      <c r="E63">
+        <v>-93.8420000000001</v>
+      </c>
+      <c r="F63">
+        <v>944.1579999999999</v>
+      </c>
+      <c r="G63">
+        <v>557.9</v>
+      </c>
+      <c r="H63">
+        <v>509.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>121.5</v>
+      </c>
+      <c r="K63">
+        <v>141.3</v>
+      </c>
+      <c r="L63">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M63">
+        <v>225.4649304</v>
+      </c>
+      <c r="N63">
+        <v>-245.2649304</v>
+      </c>
+      <c r="O63">
+        <v>-53.95828468799999</v>
+      </c>
+      <c r="P63">
+        <v>-191.306645712</v>
+      </c>
+      <c r="Q63">
+        <v>-50.00664571199999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2802998672174956</v>
+      </c>
+      <c r="T63">
+        <v>1.992293660415901</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.01932007781552533</v>
+      </c>
+      <c r="W63">
+        <v>0.2434136345823475</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.08781853552511509</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2597992653100553</v>
+      </c>
+      <c r="C64">
+        <v>64.10270977718687</v>
+      </c>
+      <c r="D64">
+        <v>465.8387097771869</v>
+      </c>
+      <c r="E64">
+        <v>-78.36400000000003</v>
+      </c>
+      <c r="F64">
+        <v>959.636</v>
+      </c>
+      <c r="G64">
+        <v>557.9</v>
+      </c>
+      <c r="H64">
+        <v>509.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>121.5</v>
+      </c>
+      <c r="K64">
+        <v>141.3</v>
+      </c>
+      <c r="L64">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M64">
+        <v>229.1610768</v>
+      </c>
+      <c r="N64">
+        <v>-248.9610768</v>
+      </c>
+      <c r="O64">
+        <v>-54.771436896</v>
+      </c>
+      <c r="P64">
+        <v>-194.189639904</v>
+      </c>
+      <c r="Q64">
+        <v>-52.88963990400003</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2866551268811139</v>
+      </c>
+      <c r="T64">
+        <v>2.044722440953161</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.0190084636572104</v>
+      </c>
+      <c r="W64">
+        <v>0.2433392211213418</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.08640210753277455</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2617992653100553</v>
+      </c>
+      <c r="C65">
+        <v>44.54714539377233</v>
+      </c>
+      <c r="D65">
+        <v>461.7611453937724</v>
+      </c>
+      <c r="E65">
+        <v>-62.88599999999997</v>
+      </c>
+      <c r="F65">
+        <v>975.114</v>
+      </c>
+      <c r="G65">
+        <v>557.9</v>
+      </c>
+      <c r="H65">
+        <v>509.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>121.5</v>
+      </c>
+      <c r="K65">
+        <v>141.3</v>
+      </c>
+      <c r="L65">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M65">
+        <v>232.8572232</v>
+      </c>
+      <c r="N65">
+        <v>-252.6572232</v>
+      </c>
+      <c r="O65">
+        <v>-55.584589104</v>
+      </c>
+      <c r="P65">
+        <v>-197.072634096</v>
+      </c>
+      <c r="Q65">
+        <v>-55.77263409600002</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.293353914094117</v>
+      </c>
+      <c r="T65">
+        <v>2.099985209627571</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.01870674201185785</v>
+      </c>
+      <c r="W65">
+        <v>0.2432671699924317</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.08503064550844486</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2637992653100552</v>
+      </c>
+      <c r="C66">
+        <v>25.06234481325293</v>
+      </c>
+      <c r="D66">
+        <v>457.7543448132529</v>
+      </c>
+      <c r="E66">
+        <v>-47.40800000000002</v>
+      </c>
+      <c r="F66">
+        <v>990.592</v>
+      </c>
+      <c r="G66">
+        <v>557.9</v>
+      </c>
+      <c r="H66">
+        <v>509.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>121.5</v>
+      </c>
+      <c r="K66">
+        <v>141.3</v>
+      </c>
+      <c r="L66">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M66">
+        <v>236.5533696</v>
+      </c>
+      <c r="N66">
+        <v>-256.3533696</v>
+      </c>
+      <c r="O66">
+        <v>-56.39774131199999</v>
+      </c>
+      <c r="P66">
+        <v>-199.955628288</v>
+      </c>
+      <c r="Q66">
+        <v>-58.655628288</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3004248561522869</v>
+      </c>
+      <c r="T66">
+        <v>2.158318132117226</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.01841444916792258</v>
+      </c>
+      <c r="W66">
+        <v>0.2431973704612999</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.08370204167237527</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2657992653100553</v>
+      </c>
+      <c r="C67">
+        <v>5.646481784279217</v>
+      </c>
+      <c r="D67">
+        <v>453.8164817842792</v>
+      </c>
+      <c r="E67">
+        <v>-31.92999999999995</v>
+      </c>
+      <c r="F67">
+        <v>1006.07</v>
+      </c>
+      <c r="G67">
+        <v>557.9</v>
+      </c>
+      <c r="H67">
+        <v>509.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>121.5</v>
+      </c>
+      <c r="K67">
+        <v>141.3</v>
+      </c>
+      <c r="L67">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M67">
+        <v>240.249516</v>
+      </c>
+      <c r="N67">
+        <v>-260.049516</v>
+      </c>
+      <c r="O67">
+        <v>-57.21089352</v>
+      </c>
+      <c r="P67">
+        <v>-202.83862248</v>
+      </c>
+      <c r="Q67">
+        <v>-61.53862248000002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3078998520423523</v>
+      </c>
+      <c r="T67">
+        <v>2.219984364463433</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.01813114994995453</v>
+      </c>
+      <c r="W67">
+        <v>0.2431297186080492</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.08241431795433884</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2677992653100552</v>
+      </c>
+      <c r="C68">
+        <v>-13.70220763867894</v>
+      </c>
+      <c r="D68">
+        <v>449.9457923613211</v>
+      </c>
+      <c r="E68">
+        <v>-16.452</v>
+      </c>
+      <c r="F68">
+        <v>1021.548</v>
+      </c>
+      <c r="G68">
+        <v>557.9</v>
+      </c>
+      <c r="H68">
+        <v>509.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>121.5</v>
+      </c>
+      <c r="K68">
+        <v>141.3</v>
+      </c>
+      <c r="L68">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M68">
+        <v>243.9456624</v>
+      </c>
+      <c r="N68">
+        <v>-263.7456624</v>
+      </c>
+      <c r="O68">
+        <v>-58.024045728</v>
+      </c>
+      <c r="P68">
+        <v>-205.721616672</v>
+      </c>
+      <c r="Q68">
+        <v>-64.421616672</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3158145535730097</v>
+      </c>
+      <c r="T68">
+        <v>2.285278022241769</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.01785643555677341</v>
+      </c>
+      <c r="W68">
+        <v>0.2430641168109575</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.0811656161671519</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2697992653100553</v>
+      </c>
+      <c r="C69">
+        <v>-32.9854277299562</v>
+      </c>
+      <c r="D69">
+        <v>446.1405722700439</v>
+      </c>
+      <c r="E69">
+        <v>-0.9739999999999327</v>
+      </c>
+      <c r="F69">
+        <v>1037.026</v>
+      </c>
+      <c r="G69">
+        <v>557.9</v>
+      </c>
+      <c r="H69">
+        <v>509.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>121.5</v>
+      </c>
+      <c r="K69">
+        <v>141.3</v>
+      </c>
+      <c r="L69">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M69">
+        <v>247.6418088</v>
+      </c>
+      <c r="N69">
+        <v>-267.4418088</v>
+      </c>
+      <c r="O69">
+        <v>-58.837197936</v>
+      </c>
+      <c r="P69">
+        <v>-208.6046108640001</v>
+      </c>
+      <c r="Q69">
+        <v>-67.30461086400004</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3242089339843131</v>
+      </c>
+      <c r="T69">
+        <v>2.354528871400611</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.01758992159323948</v>
+      </c>
+      <c r="W69">
+        <v>0.2430004732764656</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.07995418906017937</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2717992653100553</v>
+      </c>
+      <c r="C70">
+        <v>-52.20482559474499</v>
+      </c>
+      <c r="D70">
+        <v>442.3991744052552</v>
+      </c>
+      <c r="E70">
+        <v>14.50400000000013</v>
+      </c>
+      <c r="F70">
+        <v>1052.504</v>
+      </c>
+      <c r="G70">
+        <v>557.9</v>
+      </c>
+      <c r="H70">
+        <v>509.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>121.5</v>
+      </c>
+      <c r="K70">
+        <v>141.3</v>
+      </c>
+      <c r="L70">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M70">
+        <v>251.3379552</v>
+      </c>
+      <c r="N70">
+        <v>-271.1379552000001</v>
+      </c>
+      <c r="O70">
+        <v>-59.65035014400001</v>
+      </c>
+      <c r="P70">
+        <v>-211.4876050560001</v>
+      </c>
+      <c r="Q70">
+        <v>-70.18760505600005</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3331279631713228</v>
+      </c>
+      <c r="T70">
+        <v>2.428107898631879</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.01733124627569184</v>
+      </c>
+      <c r="W70">
+        <v>0.2429387016106352</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.07877839216223581</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2737992653100552</v>
+      </c>
+      <c r="C71">
+        <v>-71.36199354630321</v>
+      </c>
+      <c r="D71">
+        <v>438.7200064536968</v>
+      </c>
+      <c r="E71">
+        <v>29.98199999999997</v>
+      </c>
+      <c r="F71">
+        <v>1067.982</v>
+      </c>
+      <c r="G71">
+        <v>557.9</v>
+      </c>
+      <c r="H71">
+        <v>509.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>121.5</v>
+      </c>
+      <c r="K71">
+        <v>141.3</v>
+      </c>
+      <c r="L71">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M71">
+        <v>255.0341016</v>
+      </c>
+      <c r="N71">
+        <v>-274.8341016000001</v>
+      </c>
+      <c r="O71">
+        <v>-60.46350235200001</v>
+      </c>
+      <c r="P71">
+        <v>-214.370599248</v>
+      </c>
+      <c r="Q71">
+        <v>-73.07059924800004</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3426224135962042</v>
+      </c>
+      <c r="T71">
+        <v>2.506433959878069</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.01708006879343543</v>
+      </c>
+      <c r="W71">
+        <v>0.2428787204278724</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.07763667633379745</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2757992653100553</v>
+      </c>
+      <c r="C72">
+        <v>-90.45847136552209</v>
+      </c>
+      <c r="D72">
+        <v>435.101528634478</v>
+      </c>
+      <c r="E72">
+        <v>45.46000000000004</v>
+      </c>
+      <c r="F72">
+        <v>1083.46</v>
+      </c>
+      <c r="G72">
+        <v>557.9</v>
+      </c>
+      <c r="H72">
+        <v>509.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>121.5</v>
+      </c>
+      <c r="K72">
+        <v>141.3</v>
+      </c>
+      <c r="L72">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M72">
+        <v>258.730248</v>
+      </c>
+      <c r="N72">
+        <v>-278.530248</v>
+      </c>
+      <c r="O72">
+        <v>-61.27665456</v>
+      </c>
+      <c r="P72">
+        <v>-217.25359344</v>
+      </c>
+      <c r="Q72">
+        <v>-75.95359344000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3527498273827444</v>
+      </c>
+      <c r="T72">
+        <v>2.589981758540671</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.01683606781067207</v>
+      </c>
+      <c r="W72">
+        <v>0.2428204529931885</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.07652758095760026</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2777992653100553</v>
+      </c>
+      <c r="C73">
+        <v>-109.4957484495854</v>
+      </c>
+      <c r="D73">
+        <v>431.5422515504144</v>
+      </c>
+      <c r="E73">
+        <v>60.93799999999987</v>
+      </c>
+      <c r="F73">
+        <v>1098.938</v>
+      </c>
+      <c r="G73">
+        <v>557.9</v>
+      </c>
+      <c r="H73">
+        <v>509.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>121.5</v>
+      </c>
+      <c r="K73">
+        <v>141.3</v>
+      </c>
+      <c r="L73">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M73">
+        <v>262.4263944</v>
+      </c>
+      <c r="N73">
+        <v>-282.2263944</v>
+      </c>
+      <c r="O73">
+        <v>-62.089806768</v>
+      </c>
+      <c r="P73">
+        <v>-220.136587632</v>
+      </c>
+      <c r="Q73">
+        <v>-78.836587632</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3635756834993907</v>
+      </c>
+      <c r="T73">
+        <v>2.679291474352418</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.0165989400950288</v>
+      </c>
+      <c r="W73">
+        <v>0.2427638268946929</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.07544972770467639</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2797992653100553</v>
+      </c>
+      <c r="C74">
+        <v>-128.4752658560304</v>
+      </c>
+      <c r="D74">
+        <v>428.0407341439695</v>
+      </c>
+      <c r="E74">
+        <v>76.41599999999994</v>
+      </c>
+      <c r="F74">
+        <v>1114.416</v>
+      </c>
+      <c r="G74">
+        <v>557.9</v>
+      </c>
+      <c r="H74">
+        <v>509.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>121.5</v>
+      </c>
+      <c r="K74">
+        <v>141.3</v>
+      </c>
+      <c r="L74">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M74">
+        <v>266.1225408</v>
+      </c>
+      <c r="N74">
+        <v>-285.9225408</v>
+      </c>
+      <c r="O74">
+        <v>-62.902958976</v>
+      </c>
+      <c r="P74">
+        <v>-223.019581824</v>
+      </c>
+      <c r="Q74">
+        <v>-81.71958182400002</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3751748150529403</v>
+      </c>
+      <c r="T74">
+        <v>2.77498045557929</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.01636839926037562</v>
+      </c>
+      <c r="W74">
+        <v>0.2427087737433777</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.07440181481988928</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2817992653100552</v>
+      </c>
+      <c r="C75">
+        <v>-147.3984182480904</v>
+      </c>
+      <c r="D75">
+        <v>424.5955817519096</v>
+      </c>
+      <c r="E75">
+        <v>91.89400000000001</v>
+      </c>
+      <c r="F75">
+        <v>1129.894</v>
+      </c>
+      <c r="G75">
+        <v>557.9</v>
+      </c>
+      <c r="H75">
+        <v>509.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>121.5</v>
+      </c>
+      <c r="K75">
+        <v>141.3</v>
+      </c>
+      <c r="L75">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M75">
+        <v>269.8186872</v>
+      </c>
+      <c r="N75">
+        <v>-289.6186872</v>
+      </c>
+      <c r="O75">
+        <v>-63.71611118399999</v>
+      </c>
+      <c r="P75">
+        <v>-225.902576016</v>
+      </c>
+      <c r="Q75">
+        <v>-84.602576016</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3876331415363825</v>
+      </c>
+      <c r="T75">
+        <v>2.877757509489634</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.01614417461297322</v>
+      </c>
+      <c r="W75">
+        <v>0.242655228897578</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.073382611877151</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2837992653100552</v>
+      </c>
+      <c r="C76">
+        <v>-166.2665557468486</v>
+      </c>
+      <c r="D76">
+        <v>421.2054442531514</v>
+      </c>
+      <c r="E76">
+        <v>107.3719999999998</v>
+      </c>
+      <c r="F76">
+        <v>1145.372</v>
+      </c>
+      <c r="G76">
+        <v>557.9</v>
+      </c>
+      <c r="H76">
+        <v>509.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>121.5</v>
+      </c>
+      <c r="K76">
+        <v>141.3</v>
+      </c>
+      <c r="L76">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M76">
+        <v>273.5148336</v>
+      </c>
+      <c r="N76">
+        <v>-293.3148336</v>
+      </c>
+      <c r="O76">
+        <v>-64.52926339199999</v>
+      </c>
+      <c r="P76">
+        <v>-228.785570208</v>
+      </c>
+      <c r="Q76">
+        <v>-87.48557020799998</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4010498008262434</v>
+      </c>
+      <c r="T76">
+        <v>2.988440490623851</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.01592601009117629</v>
+      </c>
+      <c r="W76">
+        <v>0.2426031312097729</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.07239095495989223</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2857992653100552</v>
+      </c>
+      <c r="C77">
+        <v>-185.0809856953613</v>
+      </c>
+      <c r="D77">
+        <v>417.8690143046387</v>
+      </c>
+      <c r="E77">
+        <v>122.8499999999999</v>
+      </c>
+      <c r="F77">
+        <v>1160.85</v>
+      </c>
+      <c r="G77">
+        <v>557.9</v>
+      </c>
+      <c r="H77">
+        <v>509.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>121.5</v>
+      </c>
+      <c r="K77">
+        <v>141.3</v>
+      </c>
+      <c r="L77">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M77">
+        <v>277.21098</v>
+      </c>
+      <c r="N77">
+        <v>-297.01098</v>
+      </c>
+      <c r="O77">
+        <v>-65.3424156</v>
+      </c>
+      <c r="P77">
+        <v>-231.6685644</v>
+      </c>
+      <c r="Q77">
+        <v>-90.36856440000003</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4155397928592932</v>
+      </c>
+      <c r="T77">
+        <v>3.107978110248805</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.0157136632899606</v>
+      </c>
+      <c r="W77">
+        <v>0.2425524227936426</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.07142574222709364</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2877992653100552</v>
+      </c>
+      <c r="C78">
+        <v>-203.8429743395988</v>
+      </c>
+      <c r="D78">
+        <v>414.5850256604012</v>
+      </c>
+      <c r="E78">
+        <v>138.328</v>
+      </c>
+      <c r="F78">
+        <v>1176.328</v>
+      </c>
+      <c r="G78">
+        <v>557.9</v>
+      </c>
+      <c r="H78">
+        <v>509.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>121.5</v>
+      </c>
+      <c r="K78">
+        <v>141.3</v>
+      </c>
+      <c r="L78">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M78">
+        <v>280.9071264</v>
+      </c>
+      <c r="N78">
+        <v>-300.7071264</v>
+      </c>
+      <c r="O78">
+        <v>-66.15556780799999</v>
+      </c>
+      <c r="P78">
+        <v>-234.551558592</v>
+      </c>
+      <c r="Q78">
+        <v>-93.25155859199998</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4312372842284304</v>
+      </c>
+      <c r="T78">
+        <v>3.237477198175839</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.01550690456246112</v>
+      </c>
+      <c r="W78">
+        <v>0.2425030488095157</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.07048592982936874</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2897992653100552</v>
+      </c>
+      <c r="C79">
+        <v>-222.5537484307405</v>
+      </c>
+      <c r="D79">
+        <v>411.3522515692596</v>
+      </c>
+      <c r="E79">
+        <v>153.806</v>
+      </c>
+      <c r="F79">
+        <v>1191.806</v>
+      </c>
+      <c r="G79">
+        <v>557.9</v>
+      </c>
+      <c r="H79">
+        <v>509.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>121.5</v>
+      </c>
+      <c r="K79">
+        <v>141.3</v>
+      </c>
+      <c r="L79">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M79">
+        <v>284.6032728</v>
+      </c>
+      <c r="N79">
+        <v>-304.4032728</v>
+      </c>
+      <c r="O79">
+        <v>-66.96872001599999</v>
+      </c>
+      <c r="P79">
+        <v>-237.434552784</v>
+      </c>
+      <c r="Q79">
+        <v>-96.13455278400002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4482997748470577</v>
+      </c>
+      <c r="T79">
+        <v>3.378237076357397</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.01530551619152006</v>
+      </c>
+      <c r="W79">
+        <v>0.242454957266535</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.06957052814327302</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2917992653100553</v>
+      </c>
+      <c r="C80">
+        <v>-241.2144967530875</v>
+      </c>
+      <c r="D80">
+        <v>408.1695032469127</v>
+      </c>
+      <c r="E80">
+        <v>169.2840000000001</v>
+      </c>
+      <c r="F80">
+        <v>1207.284</v>
+      </c>
+      <c r="G80">
+        <v>557.9</v>
+      </c>
+      <c r="H80">
+        <v>509.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>121.5</v>
+      </c>
+      <c r="K80">
+        <v>141.3</v>
+      </c>
+      <c r="L80">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M80">
+        <v>288.2994192</v>
+      </c>
+      <c r="N80">
+        <v>-308.0994192000001</v>
+      </c>
+      <c r="O80">
+        <v>-67.78187222400001</v>
+      </c>
+      <c r="P80">
+        <v>-240.317546976</v>
+      </c>
+      <c r="Q80">
+        <v>-99.01754697600003</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4669134009764696</v>
+      </c>
+      <c r="T80">
+        <v>3.531793307100916</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.01510929162496211</v>
+      </c>
+      <c r="W80">
+        <v>0.242408098840041</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.06867859829528244</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2937992653100553</v>
+      </c>
+      <c r="C81">
+        <v>-259.8263715815865</v>
+      </c>
+      <c r="D81">
+        <v>405.0356284184134</v>
+      </c>
+      <c r="E81">
+        <v>184.7619999999999</v>
+      </c>
+      <c r="F81">
+        <v>1222.762</v>
+      </c>
+      <c r="G81">
+        <v>557.9</v>
+      </c>
+      <c r="H81">
+        <v>509.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>121.5</v>
+      </c>
+      <c r="K81">
+        <v>141.3</v>
+      </c>
+      <c r="L81">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M81">
+        <v>291.9955656</v>
+      </c>
+      <c r="N81">
+        <v>-311.7955656</v>
+      </c>
+      <c r="O81">
+        <v>-68.595024432</v>
+      </c>
+      <c r="P81">
+        <v>-243.200541168</v>
+      </c>
+      <c r="Q81">
+        <v>-101.900541168</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4872997534039206</v>
+      </c>
+      <c r="T81">
+        <v>3.699973940772388</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.01491803476894994</v>
+      </c>
+      <c r="W81">
+        <v>0.2423624267028253</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.06780924894977236</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2957992653100552</v>
+      </c>
+      <c r="C82">
+        <v>-278.3904900727241</v>
+      </c>
+      <c r="D82">
+        <v>401.949509927276</v>
+      </c>
+      <c r="E82">
+        <v>200.24</v>
+      </c>
+      <c r="F82">
+        <v>1238.24</v>
+      </c>
+      <c r="G82">
+        <v>557.9</v>
+      </c>
+      <c r="H82">
+        <v>509.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>121.5</v>
+      </c>
+      <c r="K82">
+        <v>141.3</v>
+      </c>
+      <c r="L82">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M82">
+        <v>295.691712</v>
+      </c>
+      <c r="N82">
+        <v>-315.491712</v>
+      </c>
+      <c r="O82">
+        <v>-69.40817663999999</v>
+      </c>
+      <c r="P82">
+        <v>-246.08353536</v>
+      </c>
+      <c r="Q82">
+        <v>-104.78353536</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5097247410741166</v>
+      </c>
+      <c r="T82">
+        <v>3.884972637811007</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.01473155933433806</v>
+      </c>
+      <c r="W82">
+        <v>0.2423178963690399</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.06696163333790039</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2977992653100553</v>
+      </c>
+      <c r="C83">
+        <v>-296.9079355923111</v>
+      </c>
+      <c r="D83">
+        <v>398.910064407689</v>
+      </c>
+      <c r="E83">
+        <v>215.7180000000001</v>
+      </c>
+      <c r="F83">
+        <v>1253.718</v>
+      </c>
+      <c r="G83">
+        <v>557.9</v>
+      </c>
+      <c r="H83">
+        <v>509.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>121.5</v>
+      </c>
+      <c r="K83">
+        <v>141.3</v>
+      </c>
+      <c r="L83">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M83">
+        <v>299.3878584</v>
+      </c>
+      <c r="N83">
+        <v>-319.1878584</v>
+      </c>
+      <c r="O83">
+        <v>-70.221328848</v>
+      </c>
+      <c r="P83">
+        <v>-248.9665295520001</v>
+      </c>
+      <c r="Q83">
+        <v>-107.666529552</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5345102537622279</v>
+      </c>
+      <c r="T83">
+        <v>4.089444881906323</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.014549688231445</v>
+      </c>
+      <c r="W83">
+        <v>0.2422744655496691</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.06613494650656815</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2997992653100553</v>
+      </c>
+      <c r="C84">
+        <v>-315.3797589834807</v>
+      </c>
+      <c r="D84">
+        <v>395.9162410165195</v>
+      </c>
+      <c r="E84">
+        <v>231.1960000000001</v>
+      </c>
+      <c r="F84">
+        <v>1269.196</v>
+      </c>
+      <c r="G84">
+        <v>557.9</v>
+      </c>
+      <c r="H84">
+        <v>509.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>121.5</v>
+      </c>
+      <c r="K84">
+        <v>141.3</v>
+      </c>
+      <c r="L84">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M84">
+        <v>303.0840048000001</v>
+      </c>
+      <c r="N84">
+        <v>-322.8840048000001</v>
+      </c>
+      <c r="O84">
+        <v>-71.034481056</v>
+      </c>
+      <c r="P84">
+        <v>-251.8495237440001</v>
+      </c>
+      <c r="Q84">
+        <v>-110.5495237440001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.562049712304574</v>
+      </c>
+      <c r="T84">
+        <v>4.316636264234454</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.0143722530091103</v>
+      </c>
+      <c r="W84">
+        <v>0.2422320940185756</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.06532842276868323</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3017992653100552</v>
+      </c>
+      <c r="C85">
+        <v>-333.8069797780111</v>
+      </c>
+      <c r="D85">
+        <v>392.9670202219889</v>
+      </c>
+      <c r="E85">
+        <v>246.674</v>
+      </c>
+      <c r="F85">
+        <v>1284.674</v>
+      </c>
+      <c r="G85">
+        <v>557.9</v>
+      </c>
+      <c r="H85">
+        <v>509.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>121.5</v>
+      </c>
+      <c r="K85">
+        <v>141.3</v>
+      </c>
+      <c r="L85">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M85">
+        <v>306.7801512</v>
+      </c>
+      <c r="N85">
+        <v>-326.5801512</v>
+      </c>
+      <c r="O85">
+        <v>-71.847633264</v>
+      </c>
+      <c r="P85">
+        <v>-254.7325179360001</v>
+      </c>
+      <c r="Q85">
+        <v>-113.432517936</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5928291071460194</v>
+      </c>
+      <c r="T85">
+        <v>4.570556044483538</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.01419909333430174</v>
+      </c>
+      <c r="W85">
+        <v>0.2421907434882312</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.06454133333773515</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3037992653100552</v>
+      </c>
+      <c r="C86">
+        <v>-352.190587353912</v>
+      </c>
+      <c r="D86">
+        <v>390.0614126460878</v>
+      </c>
+      <c r="E86">
+        <v>262.1519999999998</v>
+      </c>
+      <c r="F86">
+        <v>1300.152</v>
+      </c>
+      <c r="G86">
+        <v>557.9</v>
+      </c>
+      <c r="H86">
+        <v>509.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>121.5</v>
+      </c>
+      <c r="K86">
+        <v>141.3</v>
+      </c>
+      <c r="L86">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M86">
+        <v>310.4762976</v>
+      </c>
+      <c r="N86">
+        <v>-330.2762976</v>
+      </c>
+      <c r="O86">
+        <v>-72.66078547199999</v>
+      </c>
+      <c r="P86">
+        <v>-257.615512128</v>
+      </c>
+      <c r="Q86">
+        <v>-116.315512128</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6274559263426456</v>
+      </c>
+      <c r="T86">
+        <v>4.856215797263758</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.01403005650889339</v>
+      </c>
+      <c r="W86">
+        <v>0.2421503774943237</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.0637729841313337</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3057992653100552</v>
+      </c>
+      <c r="C87">
+        <v>-370.5315420420291</v>
+      </c>
+      <c r="D87">
+        <v>387.1984579579709</v>
+      </c>
+      <c r="E87">
+        <v>277.6299999999999</v>
+      </c>
+      <c r="F87">
+        <v>1315.63</v>
+      </c>
+      <c r="G87">
+        <v>557.9</v>
+      </c>
+      <c r="H87">
+        <v>509.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>121.5</v>
+      </c>
+      <c r="K87">
+        <v>141.3</v>
+      </c>
+      <c r="L87">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M87">
+        <v>314.172444</v>
+      </c>
+      <c r="N87">
+        <v>-333.972444</v>
+      </c>
+      <c r="O87">
+        <v>-73.47393767999999</v>
+      </c>
+      <c r="P87">
+        <v>-260.49850632</v>
+      </c>
+      <c r="Q87">
+        <v>-119.19850632</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6666996547654884</v>
+      </c>
+      <c r="T87">
+        <v>5.179963517081341</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.01386499702055347</v>
+      </c>
+      <c r="W87">
+        <v>0.2421109612885082</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.06302271372978852</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3077992653100552</v>
+      </c>
+      <c r="C88">
+        <v>-388.8307761842718</v>
+      </c>
+      <c r="D88">
+        <v>384.3772238157281</v>
+      </c>
+      <c r="E88">
+        <v>293.1079999999999</v>
+      </c>
+      <c r="F88">
+        <v>1331.108</v>
+      </c>
+      <c r="G88">
+        <v>557.9</v>
+      </c>
+      <c r="H88">
+        <v>509.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>121.5</v>
+      </c>
+      <c r="K88">
+        <v>141.3</v>
+      </c>
+      <c r="L88">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M88">
+        <v>317.8685904</v>
+      </c>
+      <c r="N88">
+        <v>-337.6685904</v>
+      </c>
+      <c r="O88">
+        <v>-74.287089888</v>
+      </c>
+      <c r="P88">
+        <v>-263.381500512</v>
+      </c>
+      <c r="Q88">
+        <v>-122.081500512</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.7115496301058806</v>
+      </c>
+      <c r="T88">
+        <v>5.54996091115858</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.01370377612496564</v>
+      </c>
+      <c r="W88">
+        <v>0.2420724617386418</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.06228989147711661</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3097992653100552</v>
+      </c>
+      <c r="C89">
+        <v>-407.0891951459146</v>
+      </c>
+      <c r="D89">
+        <v>381.5968048540855</v>
+      </c>
+      <c r="E89">
+        <v>308.586</v>
+      </c>
+      <c r="F89">
+        <v>1346.586</v>
+      </c>
+      <c r="G89">
+        <v>557.9</v>
+      </c>
+      <c r="H89">
+        <v>509.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>121.5</v>
+      </c>
+      <c r="K89">
+        <v>141.3</v>
+      </c>
+      <c r="L89">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M89">
+        <v>321.5647368</v>
+      </c>
+      <c r="N89">
+        <v>-341.3647368</v>
+      </c>
+      <c r="O89">
+        <v>-75.10024209599999</v>
+      </c>
+      <c r="P89">
+        <v>-266.264494704</v>
+      </c>
+      <c r="Q89">
+        <v>-124.964494704</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7632996016524869</v>
+      </c>
+      <c r="T89">
+        <v>5.976880981247702</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.01354626145686259</v>
+      </c>
+      <c r="W89">
+        <v>0.2420348472358988</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.06157391571301174</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3117992653100552</v>
+      </c>
+      <c r="C90">
+        <v>-425.3076782842743</v>
+      </c>
+      <c r="D90">
+        <v>378.8563217157258</v>
+      </c>
+      <c r="E90">
+        <v>324.0640000000001</v>
+      </c>
+      <c r="F90">
+        <v>1362.064</v>
+      </c>
+      <c r="G90">
+        <v>557.9</v>
+      </c>
+      <c r="H90">
+        <v>509.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>121.5</v>
+      </c>
+      <c r="K90">
+        <v>141.3</v>
+      </c>
+      <c r="L90">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M90">
+        <v>325.2608832</v>
+      </c>
+      <c r="N90">
+        <v>-345.0608832</v>
+      </c>
+      <c r="O90">
+        <v>-75.91339430399999</v>
+      </c>
+      <c r="P90">
+        <v>-269.147488896</v>
+      </c>
+      <c r="Q90">
+        <v>-127.847488896</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.8236745684568607</v>
+      </c>
+      <c r="T90">
+        <v>6.474954396351677</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.01339232666758006</v>
+      </c>
+      <c r="W90">
+        <v>0.2419980876082181</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.06087421212536381</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3137992653100552</v>
+      </c>
+      <c r="C91">
+        <v>-443.4870798759496</v>
+      </c>
+      <c r="D91">
+        <v>376.1549201240504</v>
+      </c>
+      <c r="E91">
+        <v>339.5419999999999</v>
+      </c>
+      <c r="F91">
+        <v>1377.542</v>
+      </c>
+      <c r="G91">
+        <v>557.9</v>
+      </c>
+      <c r="H91">
+        <v>509.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>121.5</v>
+      </c>
+      <c r="K91">
+        <v>141.3</v>
+      </c>
+      <c r="L91">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M91">
+        <v>328.9570296</v>
+      </c>
+      <c r="N91">
+        <v>-348.7570296</v>
+      </c>
+      <c r="O91">
+        <v>-76.726546512</v>
+      </c>
+      <c r="P91">
+        <v>-272.030483088</v>
+      </c>
+      <c r="Q91">
+        <v>-130.730483088</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.895026801952939</v>
+      </c>
+      <c r="T91">
+        <v>7.06358661420183</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.01324185108704545</v>
+      </c>
+      <c r="W91">
+        <v>0.2419621540395864</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.06019023221384301</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3157992653100552</v>
+      </c>
+      <c r="C92">
+        <v>-461.628230004668</v>
+      </c>
+      <c r="D92">
+        <v>373.491769995332</v>
+      </c>
+      <c r="E92">
+        <v>355.02</v>
+      </c>
+      <c r="F92">
+        <v>1393.02</v>
+      </c>
+      <c r="G92">
+        <v>557.9</v>
+      </c>
+      <c r="H92">
+        <v>509.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>121.5</v>
+      </c>
+      <c r="K92">
+        <v>141.3</v>
+      </c>
+      <c r="L92">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M92">
+        <v>332.653176</v>
+      </c>
+      <c r="N92">
+        <v>-352.453176</v>
+      </c>
+      <c r="O92">
+        <v>-77.53969872</v>
+      </c>
+      <c r="P92">
+        <v>-274.9134772800001</v>
+      </c>
+      <c r="Q92">
+        <v>-133.61347728</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.980649482148233</v>
+      </c>
+      <c r="T92">
+        <v>7.769945275622014</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.0130947194083005</v>
+      </c>
+      <c r="W92">
+        <v>0.2419270189947021</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.05952145185591129</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3177992653100553</v>
+      </c>
+      <c r="C93">
+        <v>-479.7319354116848</v>
+      </c>
+      <c r="D93">
+        <v>370.8660645883152</v>
+      </c>
+      <c r="E93">
+        <v>370.498</v>
+      </c>
+      <c r="F93">
+        <v>1408.498</v>
+      </c>
+      <c r="G93">
+        <v>557.9</v>
+      </c>
+      <c r="H93">
+        <v>509.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>121.5</v>
+      </c>
+      <c r="K93">
+        <v>141.3</v>
+      </c>
+      <c r="L93">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M93">
+        <v>336.3493224</v>
+      </c>
+      <c r="N93">
+        <v>-356.1493224</v>
+      </c>
+      <c r="O93">
+        <v>-78.352850928</v>
+      </c>
+      <c r="P93">
+        <v>-277.796471472</v>
+      </c>
+      <c r="Q93">
+        <v>-136.496471472</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.085299424609148</v>
+      </c>
+      <c r="T93">
+        <v>8.633272528468906</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.01295082139282467</v>
+      </c>
+      <c r="W93">
+        <v>0.2418926561486066</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.05886736996738495</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3197992653100553</v>
+      </c>
+      <c r="C94">
+        <v>-497.798980310561</v>
+      </c>
+      <c r="D94">
+        <v>368.2770196894392</v>
+      </c>
+      <c r="E94">
+        <v>385.9760000000001</v>
+      </c>
+      <c r="F94">
+        <v>1423.976</v>
+      </c>
+      <c r="G94">
+        <v>557.9</v>
+      </c>
+      <c r="H94">
+        <v>509.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>121.5</v>
+      </c>
+      <c r="K94">
+        <v>141.3</v>
+      </c>
+      <c r="L94">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M94">
+        <v>340.0454688</v>
+      </c>
+      <c r="N94">
+        <v>-359.8454688</v>
+      </c>
+      <c r="O94">
+        <v>-79.166003136</v>
+      </c>
+      <c r="P94">
+        <v>-280.6794656640001</v>
+      </c>
+      <c r="Q94">
+        <v>-139.3794656640001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.216111852685292</v>
+      </c>
+      <c r="T94">
+        <v>9.712431594527523</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.01281005159507657</v>
+      </c>
+      <c r="W94">
+        <v>0.2418590403209043</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.05822750725034798</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3217992653100552</v>
+      </c>
+      <c r="C95">
+        <v>-515.8301271680491</v>
+      </c>
+      <c r="D95">
+        <v>365.7238728319509</v>
+      </c>
+      <c r="E95">
+        <v>401.454</v>
+      </c>
+      <c r="F95">
+        <v>1439.454</v>
+      </c>
+      <c r="G95">
+        <v>557.9</v>
+      </c>
+      <c r="H95">
+        <v>509.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>121.5</v>
+      </c>
+      <c r="K95">
+        <v>141.3</v>
+      </c>
+      <c r="L95">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M95">
+        <v>343.7416152</v>
+      </c>
+      <c r="N95">
+        <v>-363.5416152</v>
+      </c>
+      <c r="O95">
+        <v>-79.97915534399999</v>
+      </c>
+      <c r="P95">
+        <v>-283.562459856</v>
+      </c>
+      <c r="Q95">
+        <v>-142.262459856</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.384299260211762</v>
+      </c>
+      <c r="T95">
+        <v>11.09992182231717</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.01267230910480694</v>
+      </c>
+      <c r="W95">
+        <v>0.2418261474142279</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.05760140502184963</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3237992653100553</v>
+      </c>
+      <c r="C96">
+        <v>-533.8261174527236</v>
+      </c>
+      <c r="D96">
+        <v>363.2058825472764</v>
+      </c>
+      <c r="E96">
+        <v>416.932</v>
+      </c>
+      <c r="F96">
+        <v>1454.932</v>
+      </c>
+      <c r="G96">
+        <v>557.9</v>
+      </c>
+      <c r="H96">
+        <v>509.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>121.5</v>
+      </c>
+      <c r="K96">
+        <v>141.3</v>
+      </c>
+      <c r="L96">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M96">
+        <v>347.4377616</v>
+      </c>
+      <c r="N96">
+        <v>-367.2377616000001</v>
+      </c>
+      <c r="O96">
+        <v>-80.792307552</v>
+      </c>
+      <c r="P96">
+        <v>-286.445454048</v>
+      </c>
+      <c r="Q96">
+        <v>-145.145454048</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.608549136913723</v>
+      </c>
+      <c r="T96">
+        <v>12.94990879270337</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.01253749730581962</v>
+      </c>
+      <c r="W96">
+        <v>0.2417939543566298</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.05698862411736205</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3257992653100553</v>
+      </c>
+      <c r="C97">
+        <v>-551.7876723528927</v>
+      </c>
+      <c r="D97">
+        <v>360.7223276471074</v>
+      </c>
+      <c r="E97">
+        <v>432.4100000000001</v>
+      </c>
+      <c r="F97">
+        <v>1470.41</v>
+      </c>
+      <c r="G97">
+        <v>557.9</v>
+      </c>
+      <c r="H97">
+        <v>509.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>121.5</v>
+      </c>
+      <c r="K97">
+        <v>141.3</v>
+      </c>
+      <c r="L97">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M97">
+        <v>351.133908</v>
+      </c>
+      <c r="N97">
+        <v>-370.933908</v>
+      </c>
+      <c r="O97">
+        <v>-81.60545976</v>
+      </c>
+      <c r="P97">
+        <v>-289.3284482400001</v>
+      </c>
+      <c r="Q97">
+        <v>-148.02844824</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.922498964296468</v>
+      </c>
+      <c r="T97">
+        <v>15.53989055124405</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.01240552364996889</v>
+      </c>
+      <c r="W97">
+        <v>0.2417624390476126</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.05638874386349491</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3277992653100552</v>
+      </c>
+      <c r="C98">
+        <v>-569.7154934652594</v>
+      </c>
+      <c r="D98">
+        <v>358.2725065347406</v>
+      </c>
+      <c r="E98">
+        <v>447.8879999999999</v>
+      </c>
+      <c r="F98">
+        <v>1485.888</v>
+      </c>
+      <c r="G98">
+        <v>557.9</v>
+      </c>
+      <c r="H98">
+        <v>509.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>121.5</v>
+      </c>
+      <c r="K98">
+        <v>141.3</v>
+      </c>
+      <c r="L98">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M98">
+        <v>354.8300544</v>
+      </c>
+      <c r="N98">
+        <v>-374.6300544</v>
+      </c>
+      <c r="O98">
+        <v>-82.41861196799999</v>
+      </c>
+      <c r="P98">
+        <v>-292.211442432</v>
+      </c>
+      <c r="Q98">
+        <v>-150.911442432</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.39342370537058</v>
+      </c>
+      <c r="T98">
+        <v>19.42486318905501</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.01227629944528172</v>
+      </c>
+      <c r="W98">
+        <v>0.2417315803075333</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.05580136111491685</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3297992653100553</v>
+      </c>
+      <c r="C99">
+        <v>-587.6102634557103</v>
+      </c>
+      <c r="D99">
+        <v>355.8557365442898</v>
+      </c>
+      <c r="E99">
+        <v>463.366</v>
+      </c>
+      <c r="F99">
+        <v>1501.366</v>
+      </c>
+      <c r="G99">
+        <v>557.9</v>
+      </c>
+      <c r="H99">
+        <v>509.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>121.5</v>
+      </c>
+      <c r="K99">
+        <v>141.3</v>
+      </c>
+      <c r="L99">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M99">
+        <v>358.5262008</v>
+      </c>
+      <c r="N99">
+        <v>-378.3262008</v>
+      </c>
+      <c r="O99">
+        <v>-83.231764176</v>
+      </c>
+      <c r="P99">
+        <v>-295.094436624</v>
+      </c>
+      <c r="Q99">
+        <v>-153.794436624</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.178298273827441</v>
+      </c>
+      <c r="T99">
+        <v>25.89981758540669</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.01214973965718603</v>
+      </c>
+      <c r="W99">
+        <v>0.241701357830136</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.05522608935084561</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3317992653100553</v>
+      </c>
+      <c r="C100">
+        <v>-605.4726466935354</v>
+      </c>
+      <c r="D100">
+        <v>353.4713533064644</v>
+      </c>
+      <c r="E100">
+        <v>478.8439999999998</v>
+      </c>
+      <c r="F100">
+        <v>1516.844</v>
+      </c>
+      <c r="G100">
+        <v>557.9</v>
+      </c>
+      <c r="H100">
+        <v>509.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>121.5</v>
+      </c>
+      <c r="K100">
+        <v>141.3</v>
+      </c>
+      <c r="L100">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M100">
+        <v>362.2223472</v>
+      </c>
+      <c r="N100">
+        <v>-382.0223472</v>
+      </c>
+      <c r="O100">
+        <v>-84.04491638399999</v>
+      </c>
+      <c r="P100">
+        <v>-297.977430816</v>
+      </c>
+      <c r="Q100">
+        <v>-156.677430816</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.748047410741161</v>
+      </c>
+      <c r="T100">
+        <v>38.84972637811003</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.01202576272190862</v>
+      </c>
+      <c r="W100">
+        <v>0.2416717521379918</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.05466255782685736</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3337992653100553</v>
+      </c>
+      <c r="C101">
+        <v>-623.3032898603253</v>
+      </c>
+      <c r="D101">
+        <v>351.1187101396746</v>
+      </c>
+      <c r="E101">
+        <v>494.3219999999999</v>
+      </c>
+      <c r="F101">
+        <v>1532.322</v>
+      </c>
+      <c r="G101">
+        <v>557.9</v>
+      </c>
+      <c r="H101">
+        <v>509.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>121.5</v>
+      </c>
+      <c r="K101">
+        <v>141.3</v>
+      </c>
+      <c r="L101">
+        <v>-19.80000000000001</v>
+      </c>
+      <c r="M101">
+        <v>365.9184936</v>
+      </c>
+      <c r="N101">
+        <v>-385.7184936</v>
+      </c>
+      <c r="O101">
+        <v>-84.85806859199998</v>
+      </c>
+      <c r="P101">
+        <v>-300.860425008</v>
+      </c>
+      <c r="Q101">
+        <v>-159.560425008</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.457294821482321</v>
+      </c>
+      <c r="T101">
+        <v>77.69945275622007</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.01190429037118227</v>
+      </c>
+      <c r="W101">
+        <v>0.2416427445406384</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.05411041077810119</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
